--- a/sandbox-refresh-csvs/users.xlsx
+++ b/sandbox-refresh-csvs/users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chandrahas.r.bireddy\VS CODE\MOH-ALR\sandbox-refresh-csvs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00758C8A-955E-45D1-A221-C44D496998D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605F4839-B592-4A6D-8B9B-227FE3154B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dev" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="392">
   <si>
     <t>FirstName</t>
   </si>
@@ -1114,6 +1114,93 @@
   </si>
   <si>
     <t>chandT</t>
+  </si>
+  <si>
+    <t>chandra</t>
+  </si>
+  <si>
+    <t>bireddy</t>
+  </si>
+  <si>
+    <t>Hari</t>
+  </si>
+  <si>
+    <t>hpavn</t>
+  </si>
+  <si>
+    <t>nha-user@reportinguser.com</t>
+  </si>
+  <si>
+    <t>EHIS Business Admin</t>
+  </si>
+  <si>
+    <t>gandloju.vishwantha@accenture.com.business-admin</t>
+  </si>
+  <si>
+    <t>vcih-user@reportinguser.com</t>
+  </si>
+  <si>
+    <t>Mullamalla</t>
+  </si>
+  <si>
+    <t>dmull</t>
+  </si>
+  <si>
+    <t>Mariaappan</t>
+  </si>
+  <si>
+    <t>smari</t>
+  </si>
+  <si>
+    <t>Vangli</t>
+  </si>
+  <si>
+    <t>vkali</t>
+  </si>
+  <si>
+    <t>gandloju.vishwantha@accenture.com.officer</t>
+  </si>
+  <si>
+    <t>Interior</t>
+  </si>
+  <si>
+    <t>iha-user@reportinguser.com</t>
+  </si>
+  <si>
+    <t>irepo</t>
+  </si>
+  <si>
+    <t>test@reportinguser.com</t>
+  </si>
+  <si>
+    <t>vch-user@reportinguser.com</t>
+  </si>
+  <si>
+    <t>fha-user@reportinguser.com</t>
+  </si>
+  <si>
+    <t>chandrahas.r.bireddy@accenture.com.ST</t>
+  </si>
+  <si>
+    <t>david.surrao@gov.bc.ca.ST</t>
+  </si>
+  <si>
+    <t>rahul.patle@accenture.com.ST</t>
+  </si>
+  <si>
+    <t>haripavan.madireddy@accenture.com.ST</t>
+  </si>
+  <si>
+    <t>w.a.cai@accenture.com.ST</t>
+  </si>
+  <si>
+    <t>deepak.mulamalla@accenture.com.ST</t>
+  </si>
+  <si>
+    <t>senthil.k.mariappan@accenture.com.ST</t>
+  </si>
+  <si>
+    <t>v.b.kalimuthu@accenture.com.ST</t>
   </si>
 </sst>
 </file>
@@ -1137,12 +1224,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1158,9 +1251,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5135,85 +5229,647 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.796875" customWidth="1"/>
-    <col min="2" max="2" width="16.796875" customWidth="1"/>
-    <col min="3" max="3" width="34.796875" customWidth="1"/>
-    <col min="4" max="4" width="40.796875" customWidth="1"/>
-    <col min="5" max="5" width="10.796875" customWidth="1"/>
-    <col min="6" max="6" width="24.796875" customWidth="1"/>
-    <col min="7" max="7" width="32.796875" customWidth="1"/>
-    <col min="8" max="8" width="24.796875" customWidth="1"/>
-    <col min="9" max="10" width="16.796875" customWidth="1"/>
-    <col min="11" max="11" width="22.796875" customWidth="1"/>
-    <col min="12" max="12" width="12.796875" customWidth="1"/>
-    <col min="13" max="13" width="18.796875" customWidth="1"/>
-    <col min="14" max="14" width="20.796875" customWidth="1"/>
-    <col min="15" max="15" width="10.796875" customWidth="1"/>
-    <col min="16" max="16" width="28.796875" customWidth="1"/>
-    <col min="17" max="18" width="50.796875" customWidth="1"/>
-    <col min="19" max="19" width="40.796875" customWidth="1"/>
+    <col min="1" max="1" width="22.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.8984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.09765625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.8984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.8984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D3" t="s">
+        <v>385</v>
+      </c>
+      <c r="E3" t="s">
+        <v>245</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" t="s">
+        <v>386</v>
+      </c>
+      <c r="E4" t="s">
+        <v>193</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" t="b">
+        <v>1</v>
+      </c>
+      <c r="P4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>365</v>
+      </c>
+      <c r="B5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" t="s">
+        <v>387</v>
+      </c>
+      <c r="E5" t="s">
+        <v>366</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E6" t="s">
+        <v>222</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O6" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E7" t="s">
+        <v>72</v>
+      </c>
+      <c r="K7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" t="s">
+        <v>28</v>
+      </c>
+      <c r="O7" t="b">
+        <v>1</v>
+      </c>
+      <c r="P7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>368</v>
+      </c>
+      <c r="B8" t="s">
+        <v>301</v>
+      </c>
+      <c r="C8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D8" t="s">
+        <v>369</v>
+      </c>
+      <c r="E8" t="s">
+        <v>308</v>
+      </c>
+      <c r="K8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O8" t="b">
+        <v>1</v>
+      </c>
+      <c r="P8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B9" t="s">
+        <v>214</v>
+      </c>
+      <c r="C9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D9" t="s">
+        <v>370</v>
+      </c>
+      <c r="E9" t="s">
+        <v>226</v>
+      </c>
+      <c r="K9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O9" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B10" t="s">
+        <v>371</v>
+      </c>
+      <c r="C10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" t="s">
+        <v>389</v>
+      </c>
+      <c r="E10" t="s">
+        <v>372</v>
+      </c>
+      <c r="K10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" t="s">
+        <v>373</v>
+      </c>
+      <c r="C11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D11" t="s">
+        <v>390</v>
+      </c>
+      <c r="E11" t="s">
+        <v>374</v>
+      </c>
+      <c r="K11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" t="s">
+        <v>28</v>
+      </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" t="s">
+        <v>391</v>
+      </c>
+      <c r="E12" t="s">
+        <v>376</v>
+      </c>
+      <c r="K12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" t="s">
+        <v>28</v>
+      </c>
+      <c r="O12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>265</v>
+      </c>
+      <c r="B13" t="s">
+        <v>301</v>
+      </c>
+      <c r="C13" t="s">
+        <v>215</v>
+      </c>
+      <c r="D13" t="s">
+        <v>377</v>
+      </c>
+      <c r="E13" t="s">
+        <v>308</v>
+      </c>
+      <c r="K13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" t="s">
+        <v>28</v>
+      </c>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>378</v>
+      </c>
+      <c r="B14" t="s">
+        <v>214</v>
+      </c>
+      <c r="C14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D14" t="s">
+        <v>379</v>
+      </c>
+      <c r="E14" t="s">
+        <v>380</v>
+      </c>
+      <c r="K14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" t="s">
+        <v>28</v>
+      </c>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>252</v>
+      </c>
+      <c r="B15" t="s">
+        <v>253</v>
+      </c>
+      <c r="C15" t="s">
+        <v>215</v>
+      </c>
+      <c r="D15" t="s">
+        <v>381</v>
+      </c>
+      <c r="E15" t="s">
+        <v>255</v>
+      </c>
+      <c r="K15" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" t="s">
+        <v>28</v>
+      </c>
+      <c r="O15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>224</v>
+      </c>
+      <c r="B16" t="s">
+        <v>214</v>
+      </c>
+      <c r="C16" t="s">
+        <v>215</v>
+      </c>
+      <c r="D16" t="s">
+        <v>382</v>
+      </c>
+      <c r="E16" t="s">
+        <v>226</v>
+      </c>
+      <c r="K16" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" t="s">
+        <v>28</v>
+      </c>
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>213</v>
+      </c>
+      <c r="B17" t="s">
+        <v>214</v>
+      </c>
+      <c r="C17" t="s">
+        <v>215</v>
+      </c>
+      <c r="D17" t="s">
+        <v>383</v>
+      </c>
+      <c r="E17" t="s">
+        <v>217</v>
+      </c>
+      <c r="K17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O17" t="b">
+        <v>1</v>
+      </c>
+      <c r="P17" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/sandbox-refresh-csvs/users.xlsx
+++ b/sandbox-refresh-csvs/users.xlsx
@@ -8,24 +8,38 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chandrahas.r.bireddy\VS CODE\MOH-ALR\sandbox-refresh-csvs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605F4839-B592-4A6D-8B9B-227FE3154B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9FFE16-05BE-4D3A-BD43-28B2D035950F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="34620" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dev" sheetId="1" r:id="rId1"/>
     <sheet name="Dev2" sheetId="6" r:id="rId2"/>
     <sheet name="ST" sheetId="2" r:id="rId3"/>
-    <sheet name="QA" sheetId="3" r:id="rId4"/>
-    <sheet name="UAT" sheetId="4" r:id="rId5"/>
-    <sheet name="PreProd" sheetId="5" r:id="rId6"/>
+    <sheet name="UAT_Test_Users" sheetId="7" r:id="rId4"/>
+    <sheet name="QA" sheetId="3" r:id="rId5"/>
+    <sheet name="UAT" sheetId="4" r:id="rId6"/>
+    <sheet name="PreProd" sheetId="5" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2784" uniqueCount="892">
   <si>
     <t>FirstName</t>
   </si>
@@ -1201,6 +1215,1506 @@
   </si>
   <si>
     <t>v.b.kalimuthu@accenture.com.ST</t>
+  </si>
+  <si>
+    <t>Test1</t>
+  </si>
+  <si>
+    <t>nha-admin-1</t>
+  </si>
+  <si>
+    <t>phplanner@northernhealth.ca</t>
+  </si>
+  <si>
+    <t>nha-admin-1@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user1</t>
+  </si>
+  <si>
+    <t>Test2</t>
+  </si>
+  <si>
+    <t>nha-admin-2</t>
+  </si>
+  <si>
+    <t>nha-admin-2@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user2</t>
+  </si>
+  <si>
+    <t>Test3</t>
+  </si>
+  <si>
+    <t>nha-eho-1</t>
+  </si>
+  <si>
+    <t>nha-eho-1@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user6</t>
+  </si>
+  <si>
+    <t>EHIS_NHA_Water_Officer_PG</t>
+  </si>
+  <si>
+    <t>Test4</t>
+  </si>
+  <si>
+    <t>nha-eho-2</t>
+  </si>
+  <si>
+    <t>nha-eho-2@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user7</t>
+  </si>
+  <si>
+    <t>Test5</t>
+  </si>
+  <si>
+    <t>iha-admin-1</t>
+  </si>
+  <si>
+    <t>iha-admin-1@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user11</t>
+  </si>
+  <si>
+    <t>EHIS_IHA_Water_Admin_PG</t>
+  </si>
+  <si>
+    <t>Test6</t>
+  </si>
+  <si>
+    <t>iha-admin-2</t>
+  </si>
+  <si>
+    <t>iha-admin-2@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user12</t>
+  </si>
+  <si>
+    <t>Test7</t>
+  </si>
+  <si>
+    <t>iha-eho-1</t>
+  </si>
+  <si>
+    <t>iha-eho-1@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user16</t>
+  </si>
+  <si>
+    <t>EHIS_IHA_Water_Officer_PG</t>
+  </si>
+  <si>
+    <t>Test8</t>
+  </si>
+  <si>
+    <t>iha-eho-2</t>
+  </si>
+  <si>
+    <t>iha-eho-2@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user17</t>
+  </si>
+  <si>
+    <t>Test9</t>
+  </si>
+  <si>
+    <t>vch-admin-1</t>
+  </si>
+  <si>
+    <t>duncan.lu@vch.ca</t>
+  </si>
+  <si>
+    <t>vch-admin-1@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user21</t>
+  </si>
+  <si>
+    <t>EHIS_VCH_Water_Admin_PG</t>
+  </si>
+  <si>
+    <t>Test10</t>
+  </si>
+  <si>
+    <t>vch-admin-2</t>
+  </si>
+  <si>
+    <t>vch-admin-2@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user22</t>
+  </si>
+  <si>
+    <t>Test11</t>
+  </si>
+  <si>
+    <t>vch-eho-1</t>
+  </si>
+  <si>
+    <t>vch-eho-1@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user26</t>
+  </si>
+  <si>
+    <t>EHIS_VCH_Water_Officer_PG</t>
+  </si>
+  <si>
+    <t>Test12</t>
+  </si>
+  <si>
+    <t>vch-eho-2</t>
+  </si>
+  <si>
+    <t>vch-eho-2@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user27</t>
+  </si>
+  <si>
+    <t>Test13</t>
+  </si>
+  <si>
+    <t>fha-admin-1</t>
+  </si>
+  <si>
+    <t>fha-admin-1@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user31</t>
+  </si>
+  <si>
+    <t>EHIS_FHA_Water_Admin_PG</t>
+  </si>
+  <si>
+    <t>Test14</t>
+  </si>
+  <si>
+    <t>fha-eho-1</t>
+  </si>
+  <si>
+    <t>fha-eho-1@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user36</t>
+  </si>
+  <si>
+    <t>EHIS_FHA_Water_Officer_PG</t>
+  </si>
+  <si>
+    <t>Test15</t>
+  </si>
+  <si>
+    <t>viha-admin-1</t>
+  </si>
+  <si>
+    <t>natalie.kroschinsky@islandhealth.ca</t>
+  </si>
+  <si>
+    <t>viha-admin-1@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user41</t>
+  </si>
+  <si>
+    <t>EHIS_VIHA_Water_Admin_PG</t>
+  </si>
+  <si>
+    <t>Test16</t>
+  </si>
+  <si>
+    <t>viha-eho-1</t>
+  </si>
+  <si>
+    <t>viha-eho-1@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user46</t>
+  </si>
+  <si>
+    <t>EHIS_VIHA_Water_Officer_PG</t>
+  </si>
+  <si>
+    <t>Test21</t>
+  </si>
+  <si>
+    <t>hpba-admin1</t>
+  </si>
+  <si>
+    <t>alistair.stewart@gov.bc.ca</t>
+  </si>
+  <si>
+    <t>hpba-admin-1@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user64</t>
+  </si>
+  <si>
+    <t>Test22</t>
+  </si>
+  <si>
+    <t>hpba-eho-1</t>
+  </si>
+  <si>
+    <t>hpba-eho-1@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user66</t>
+  </si>
+  <si>
+    <t>EHIS_Officer_Users_PG</t>
+  </si>
+  <si>
+    <t>Test25</t>
+  </si>
+  <si>
+    <t>opho-admin-1</t>
+  </si>
+  <si>
+    <t>opho-admin-1@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user71</t>
+  </si>
+  <si>
+    <t>Test26</t>
+  </si>
+  <si>
+    <t>opho-eho-1</t>
+  </si>
+  <si>
+    <t>opho-eho-1@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user74</t>
+  </si>
+  <si>
+    <t>Test27</t>
+  </si>
+  <si>
+    <t>fha-admin-2</t>
+  </si>
+  <si>
+    <t>fha-admin-2@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>Test28</t>
+  </si>
+  <si>
+    <t>fha-eho-2</t>
+  </si>
+  <si>
+    <t>fha-eho-2@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user28</t>
+  </si>
+  <si>
+    <t>Test29</t>
+  </si>
+  <si>
+    <t>viha-admin-2</t>
+  </si>
+  <si>
+    <t>viha-admin-2@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user29</t>
+  </si>
+  <si>
+    <t>Test30</t>
+  </si>
+  <si>
+    <t>viha-eho-2</t>
+  </si>
+  <si>
+    <t>viha-eho-2@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user30</t>
+  </si>
+  <si>
+    <t>Test33</t>
+  </si>
+  <si>
+    <t>hpba-admin2</t>
+  </si>
+  <si>
+    <t>hpba-admin-2@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user33</t>
+  </si>
+  <si>
+    <t>Test34</t>
+  </si>
+  <si>
+    <t>hpba-eho-2</t>
+  </si>
+  <si>
+    <t>hpba-eho-2@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user34</t>
+  </si>
+  <si>
+    <t>Test35</t>
+  </si>
+  <si>
+    <t>opho-admin-2</t>
+  </si>
+  <si>
+    <t>opho-admin-2@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user35</t>
+  </si>
+  <si>
+    <t>Test36</t>
+  </si>
+  <si>
+    <t>opho-eho-2</t>
+  </si>
+  <si>
+    <t>opho-eho-2@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>Test37</t>
+  </si>
+  <si>
+    <t>nha-admin-3</t>
+  </si>
+  <si>
+    <t>nha-admin-3@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user37</t>
+  </si>
+  <si>
+    <t>Test38</t>
+  </si>
+  <si>
+    <t>nha-admin-4</t>
+  </si>
+  <si>
+    <t>nha-admin-4@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user38</t>
+  </si>
+  <si>
+    <t>Test39</t>
+  </si>
+  <si>
+    <t>nha-admin-5</t>
+  </si>
+  <si>
+    <t>nha-admin-5@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user39</t>
+  </si>
+  <si>
+    <t>Test40</t>
+  </si>
+  <si>
+    <t>nha-admin-6</t>
+  </si>
+  <si>
+    <t>nha-admin-6@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user40</t>
+  </si>
+  <si>
+    <t>Test41</t>
+  </si>
+  <si>
+    <t>nha-admin-7</t>
+  </si>
+  <si>
+    <t>nha-admin-7@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>Test42</t>
+  </si>
+  <si>
+    <t>nha-eho-3</t>
+  </si>
+  <si>
+    <t>nha-eho-3@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user42</t>
+  </si>
+  <si>
+    <t>Test43</t>
+  </si>
+  <si>
+    <t>nha-eho-4</t>
+  </si>
+  <si>
+    <t>nha-eho-4@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user43</t>
+  </si>
+  <si>
+    <t>Test44</t>
+  </si>
+  <si>
+    <t>nha-eho-5</t>
+  </si>
+  <si>
+    <t>nha-eho-5@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user44</t>
+  </si>
+  <si>
+    <t>Test45</t>
+  </si>
+  <si>
+    <t>nha-eho-6</t>
+  </si>
+  <si>
+    <t>nha-eho-6@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user45</t>
+  </si>
+  <si>
+    <t>Test46</t>
+  </si>
+  <si>
+    <t>nha-eho-7</t>
+  </si>
+  <si>
+    <t>nha-eho-7@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>Test47</t>
+  </si>
+  <si>
+    <t>vch-admin-3</t>
+  </si>
+  <si>
+    <t>vch-admin-3@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user47</t>
+  </si>
+  <si>
+    <t>Test48</t>
+  </si>
+  <si>
+    <t>vch-admin-4</t>
+  </si>
+  <si>
+    <t>vch-admin-4@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user48</t>
+  </si>
+  <si>
+    <t>Test49</t>
+  </si>
+  <si>
+    <t>vch-admin-5</t>
+  </si>
+  <si>
+    <t>vch-admin-5@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user49</t>
+  </si>
+  <si>
+    <t>Test50</t>
+  </si>
+  <si>
+    <t>vch-admin-6</t>
+  </si>
+  <si>
+    <t>vch-admin-6@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user50</t>
+  </si>
+  <si>
+    <t>Test51</t>
+  </si>
+  <si>
+    <t>vch-admin-7</t>
+  </si>
+  <si>
+    <t>vch-admin-7@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user51</t>
+  </si>
+  <si>
+    <t>Test52</t>
+  </si>
+  <si>
+    <t>vch-admin-8</t>
+  </si>
+  <si>
+    <t>vch-admin-8@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user52</t>
+  </si>
+  <si>
+    <t>Test53</t>
+  </si>
+  <si>
+    <t>vch-admin-9</t>
+  </si>
+  <si>
+    <t>vch-admin-9@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user53</t>
+  </si>
+  <si>
+    <t>Test54</t>
+  </si>
+  <si>
+    <t>vch-admin-10</t>
+  </si>
+  <si>
+    <t>vch-admin-10@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user54</t>
+  </si>
+  <si>
+    <t>Test55</t>
+  </si>
+  <si>
+    <t>vch-admin-11</t>
+  </si>
+  <si>
+    <t>vch-admin-11@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user55</t>
+  </si>
+  <si>
+    <t>Test56</t>
+  </si>
+  <si>
+    <t>vch-admin-12</t>
+  </si>
+  <si>
+    <t>vch-admin-12@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user56</t>
+  </si>
+  <si>
+    <t>Test57</t>
+  </si>
+  <si>
+    <t>vch-admin-13</t>
+  </si>
+  <si>
+    <t>vch-admin-13@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user57</t>
+  </si>
+  <si>
+    <t>Test58</t>
+  </si>
+  <si>
+    <t>vch-admin-14</t>
+  </si>
+  <si>
+    <t>vch-admin-14@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user58</t>
+  </si>
+  <si>
+    <t>Test59</t>
+  </si>
+  <si>
+    <t>vch-eho-3</t>
+  </si>
+  <si>
+    <t>vch-eho-3@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user59</t>
+  </si>
+  <si>
+    <t>Test60</t>
+  </si>
+  <si>
+    <t>vch-eho-4</t>
+  </si>
+  <si>
+    <t>vch-eho-4@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user60</t>
+  </si>
+  <si>
+    <t>Test61</t>
+  </si>
+  <si>
+    <t>vch-eho-5</t>
+  </si>
+  <si>
+    <t>vch-eho-5@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user61</t>
+  </si>
+  <si>
+    <t>Test62</t>
+  </si>
+  <si>
+    <t>vch-eho-6</t>
+  </si>
+  <si>
+    <t>vch-eho-6@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user62</t>
+  </si>
+  <si>
+    <t>Test63</t>
+  </si>
+  <si>
+    <t>vch-eho-7</t>
+  </si>
+  <si>
+    <t>vch-eho-7@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user63</t>
+  </si>
+  <si>
+    <t>Test64</t>
+  </si>
+  <si>
+    <t>vch-eho-8</t>
+  </si>
+  <si>
+    <t>vch-eho-8@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>Test65</t>
+  </si>
+  <si>
+    <t>vch-eho-9</t>
+  </si>
+  <si>
+    <t>vch-eho-9@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user65</t>
+  </si>
+  <si>
+    <t>Test66</t>
+  </si>
+  <si>
+    <t>vch-eho-10</t>
+  </si>
+  <si>
+    <t>vch-eho-10@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>Test67</t>
+  </si>
+  <si>
+    <t>vch-eho-11</t>
+  </si>
+  <si>
+    <t>vch-eho-11@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user67</t>
+  </si>
+  <si>
+    <t>Test68</t>
+  </si>
+  <si>
+    <t>vch-eho-12</t>
+  </si>
+  <si>
+    <t>vch-eho-12@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user68</t>
+  </si>
+  <si>
+    <t>Test70</t>
+  </si>
+  <si>
+    <t>vch-eho-14</t>
+  </si>
+  <si>
+    <t>vch-eho-14@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user70</t>
+  </si>
+  <si>
+    <t>Test71</t>
+  </si>
+  <si>
+    <t>fha-admin-3</t>
+  </si>
+  <si>
+    <t>fha-admin-3@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>Test72</t>
+  </si>
+  <si>
+    <t>fha-admin-4</t>
+  </si>
+  <si>
+    <t>fha-admin-4@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user72</t>
+  </si>
+  <si>
+    <t>Test73</t>
+  </si>
+  <si>
+    <t>fha-admin-5</t>
+  </si>
+  <si>
+    <t>fha-admin-5@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user73</t>
+  </si>
+  <si>
+    <t>Test74</t>
+  </si>
+  <si>
+    <t>fha-admin-6</t>
+  </si>
+  <si>
+    <t>fha-admin-6@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>Test75</t>
+  </si>
+  <si>
+    <t>fha-admin-7</t>
+  </si>
+  <si>
+    <t>fha-admin-7@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user75</t>
+  </si>
+  <si>
+    <t>Test76</t>
+  </si>
+  <si>
+    <t>fha-eho-18</t>
+  </si>
+  <si>
+    <t>fha-eho-18@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user76</t>
+  </si>
+  <si>
+    <t>Test77</t>
+  </si>
+  <si>
+    <t>fha-eho-19</t>
+  </si>
+  <si>
+    <t>fha-eho-19@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user77</t>
+  </si>
+  <si>
+    <t>Test78</t>
+  </si>
+  <si>
+    <t>fha-eho-20</t>
+  </si>
+  <si>
+    <t>fha-eho-20@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user78</t>
+  </si>
+  <si>
+    <t>Test79</t>
+  </si>
+  <si>
+    <t>fha-eho-21</t>
+  </si>
+  <si>
+    <t>fha-eho-21@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user79</t>
+  </si>
+  <si>
+    <t>Test80</t>
+  </si>
+  <si>
+    <t>fha-eho-22</t>
+  </si>
+  <si>
+    <t>fha-eho-22@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user80</t>
+  </si>
+  <si>
+    <t>Test81</t>
+  </si>
+  <si>
+    <t>fha-eho-23</t>
+  </si>
+  <si>
+    <t>fha-eho-23@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user81</t>
+  </si>
+  <si>
+    <t>Test82</t>
+  </si>
+  <si>
+    <t>fha-eho-24</t>
+  </si>
+  <si>
+    <t>fha-eho-24@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user82</t>
+  </si>
+  <si>
+    <t>Test83</t>
+  </si>
+  <si>
+    <t>fha-eho-25</t>
+  </si>
+  <si>
+    <t>fha-eho-25@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user83</t>
+  </si>
+  <si>
+    <t>Test84</t>
+  </si>
+  <si>
+    <t>fha-eho-26</t>
+  </si>
+  <si>
+    <t>fha-eho-26@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user84</t>
+  </si>
+  <si>
+    <t>Test85</t>
+  </si>
+  <si>
+    <t>fha-eho-27</t>
+  </si>
+  <si>
+    <t>fha-eho-27@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user85</t>
+  </si>
+  <si>
+    <t>Test86</t>
+  </si>
+  <si>
+    <t>fha-eho-3</t>
+  </si>
+  <si>
+    <t>fha-eho-3@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user86</t>
+  </si>
+  <si>
+    <t>Test87</t>
+  </si>
+  <si>
+    <t>fha-eho-4</t>
+  </si>
+  <si>
+    <t>fha-eho-4@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user87</t>
+  </si>
+  <si>
+    <t>Test88</t>
+  </si>
+  <si>
+    <t>fha-eho-5</t>
+  </si>
+  <si>
+    <t>fha-eho-5@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user88</t>
+  </si>
+  <si>
+    <t>Test89</t>
+  </si>
+  <si>
+    <t>fha-eho-6</t>
+  </si>
+  <si>
+    <t>fha-eho-6@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user89</t>
+  </si>
+  <si>
+    <t>Test90</t>
+  </si>
+  <si>
+    <t>fha-eho-7</t>
+  </si>
+  <si>
+    <t>fha-eho-7@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user90</t>
+  </si>
+  <si>
+    <t>Test91</t>
+  </si>
+  <si>
+    <t>fha-eho-8</t>
+  </si>
+  <si>
+    <t>fha-eho-8@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user91</t>
+  </si>
+  <si>
+    <t>Test92</t>
+  </si>
+  <si>
+    <t>fha-eho-9</t>
+  </si>
+  <si>
+    <t>fha-eho-9@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user92</t>
+  </si>
+  <si>
+    <t>Test93</t>
+  </si>
+  <si>
+    <t>fha-eho-10</t>
+  </si>
+  <si>
+    <t>fha-eho-10@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user93</t>
+  </si>
+  <si>
+    <t>Test94</t>
+  </si>
+  <si>
+    <t>fha-eho-11</t>
+  </si>
+  <si>
+    <t>fha-eho-11@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user94</t>
+  </si>
+  <si>
+    <t>Test95</t>
+  </si>
+  <si>
+    <t>fha-eho-12</t>
+  </si>
+  <si>
+    <t>fha-eho-12@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user95</t>
+  </si>
+  <si>
+    <t>Test96</t>
+  </si>
+  <si>
+    <t>fha-eho-13</t>
+  </si>
+  <si>
+    <t>fha-eho-13@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user96</t>
+  </si>
+  <si>
+    <t>Test97</t>
+  </si>
+  <si>
+    <t>fha-eho-14</t>
+  </si>
+  <si>
+    <t>fha-eho-14@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user97</t>
+  </si>
+  <si>
+    <t>Test98</t>
+  </si>
+  <si>
+    <t>fha-eho-15</t>
+  </si>
+  <si>
+    <t>fha-eho-15@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user98</t>
+  </si>
+  <si>
+    <t>Test99</t>
+  </si>
+  <si>
+    <t>fha-eho-16</t>
+  </si>
+  <si>
+    <t>fha-eho-16@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user99</t>
+  </si>
+  <si>
+    <t>Test100</t>
+  </si>
+  <si>
+    <t>fha-eho-17</t>
+  </si>
+  <si>
+    <t>fha-eho-17@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user100</t>
+  </si>
+  <si>
+    <t>Test101</t>
+  </si>
+  <si>
+    <t>viha-admin-3</t>
+  </si>
+  <si>
+    <t>viha-admin-3@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user101</t>
+  </si>
+  <si>
+    <t>Test102</t>
+  </si>
+  <si>
+    <t>viha-admin-4</t>
+  </si>
+  <si>
+    <t>viha-admin-4@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user102</t>
+  </si>
+  <si>
+    <t>Test103</t>
+  </si>
+  <si>
+    <t>viha-admin-5</t>
+  </si>
+  <si>
+    <t>viha-admin-5@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user103</t>
+  </si>
+  <si>
+    <t>Test104</t>
+  </si>
+  <si>
+    <t>viha-admin-6</t>
+  </si>
+  <si>
+    <t>viha-admin-6@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user104</t>
+  </si>
+  <si>
+    <t>Test105</t>
+  </si>
+  <si>
+    <t>viha-admin-7</t>
+  </si>
+  <si>
+    <t>viha-admin-7@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user105</t>
+  </si>
+  <si>
+    <t>Test106</t>
+  </si>
+  <si>
+    <t>viha-admin-8</t>
+  </si>
+  <si>
+    <t>viha-admin-8@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user106</t>
+  </si>
+  <si>
+    <t>Test107</t>
+  </si>
+  <si>
+    <t>viha-admin-9</t>
+  </si>
+  <si>
+    <t>viha-admin-9@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user107</t>
+  </si>
+  <si>
+    <t>Test108</t>
+  </si>
+  <si>
+    <t>viha-admin-10</t>
+  </si>
+  <si>
+    <t>viha-admin-10@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user108</t>
+  </si>
+  <si>
+    <t>Test109</t>
+  </si>
+  <si>
+    <t>viha-admin-11</t>
+  </si>
+  <si>
+    <t>viha-admin-11@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user109</t>
+  </si>
+  <si>
+    <t>Test110</t>
+  </si>
+  <si>
+    <t>viha-eho-3</t>
+  </si>
+  <si>
+    <t>viha-eho-3@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user110</t>
+  </si>
+  <si>
+    <t>Test111</t>
+  </si>
+  <si>
+    <t>viha-eho-4</t>
+  </si>
+  <si>
+    <t>viha-eho-4@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user111</t>
+  </si>
+  <si>
+    <t>Test112</t>
+  </si>
+  <si>
+    <t>viha-eho-5</t>
+  </si>
+  <si>
+    <t>viha-eho-5@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user112</t>
+  </si>
+  <si>
+    <t>Test113</t>
+  </si>
+  <si>
+    <t>viha-eho-6</t>
+  </si>
+  <si>
+    <t>viha-eho-6@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user113</t>
+  </si>
+  <si>
+    <t>Test114</t>
+  </si>
+  <si>
+    <t>viha-eho-7</t>
+  </si>
+  <si>
+    <t>viha-eho-7@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user114</t>
+  </si>
+  <si>
+    <t>Test115</t>
+  </si>
+  <si>
+    <t>viha-eho-8</t>
+  </si>
+  <si>
+    <t>viha-eho-8@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user115</t>
+  </si>
+  <si>
+    <t>Test116</t>
+  </si>
+  <si>
+    <t>viha-eho-9</t>
+  </si>
+  <si>
+    <t>viha-eho-9@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user116</t>
+  </si>
+  <si>
+    <t>Test117</t>
+  </si>
+  <si>
+    <t>viha-eho-10</t>
+  </si>
+  <si>
+    <t>viha-eho-10@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user117</t>
+  </si>
+  <si>
+    <t>Test118</t>
+  </si>
+  <si>
+    <t>viha-eho-11</t>
+  </si>
+  <si>
+    <t>viha-eho-11@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user118</t>
+  </si>
+  <si>
+    <t>Test121</t>
+  </si>
+  <si>
+    <t>hpba-admin3</t>
+  </si>
+  <si>
+    <t>hpba-admin-3@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user121</t>
+  </si>
+  <si>
+    <t>Test122</t>
+  </si>
+  <si>
+    <t>hpba-admin4</t>
+  </si>
+  <si>
+    <t>hpba-admin-4@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user122</t>
+  </si>
+  <si>
+    <t>Test123</t>
+  </si>
+  <si>
+    <t>hpba-eho-3</t>
+  </si>
+  <si>
+    <t>hpba-eho-3@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user123</t>
+  </si>
+  <si>
+    <t>Test124</t>
+  </si>
+  <si>
+    <t>hpba-eho-4</t>
+  </si>
+  <si>
+    <t>hpba-eho-4@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user124</t>
+  </si>
+  <si>
+    <t>Test125</t>
+  </si>
+  <si>
+    <t>viha-admin-12</t>
+  </si>
+  <si>
+    <t>viha-admin-12@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user125</t>
+  </si>
+  <si>
+    <t>Test126</t>
+  </si>
+  <si>
+    <t>viha-eho-12</t>
+  </si>
+  <si>
+    <t>viha-eho-12@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user126</t>
+  </si>
+  <si>
+    <t>Test127</t>
+  </si>
+  <si>
+    <t>viha-admin-13</t>
+  </si>
+  <si>
+    <t>viha-admin-13@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user127</t>
+  </si>
+  <si>
+    <t>Test128</t>
+  </si>
+  <si>
+    <t>viha-eho-13</t>
+  </si>
+  <si>
+    <t>viha-eho-13@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>user128</t>
+  </si>
+  <si>
+    <t>Test134</t>
+  </si>
+  <si>
+    <t>iha-eho-4</t>
+  </si>
+  <si>
+    <t>iha-eho-4@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>Test135</t>
+  </si>
+  <si>
+    <t>iha-eho-5</t>
+  </si>
+  <si>
+    <t>iha-eho-5@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>Test132</t>
+  </si>
+  <si>
+    <t>iha-admin-06</t>
+  </si>
+  <si>
+    <t>iha-admin-06@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>Test129</t>
+  </si>
+  <si>
+    <t>iha-admin-03</t>
+  </si>
+  <si>
+    <t>iha-admin-03@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>Test131</t>
+  </si>
+  <si>
+    <t>iha-admin-05</t>
+  </si>
+  <si>
+    <t>iha-admin-05@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>test131</t>
+  </si>
+  <si>
+    <t>Test130</t>
+  </si>
+  <si>
+    <t>iha-admin-04</t>
+  </si>
+  <si>
+    <t>iha-admin-04@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>test130</t>
+  </si>
+  <si>
+    <t>Test133</t>
+  </si>
+  <si>
+    <t>iha-eho-3</t>
+  </si>
+  <si>
+    <t>iha-eho-3@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>Test136</t>
+  </si>
+  <si>
+    <t>iha-eho-6</t>
+  </si>
+  <si>
+    <t>iha-eho-6@gov.bc.ca.uat</t>
   </si>
 </sst>
 </file>
@@ -5881,6 +7395,4846 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC3A407E-9EAB-4433-9358-BEF5FC974994}">
+  <dimension ref="A1:S126"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.8984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.09765625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.8984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.8984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E2" t="s">
+        <v>396</v>
+      </c>
+      <c r="K2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P2" t="s">
+        <v>120</v>
+      </c>
+      <c r="S2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C3" t="s">
+        <v>394</v>
+      </c>
+      <c r="D3" t="s">
+        <v>399</v>
+      </c>
+      <c r="E3" t="s">
+        <v>400</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" t="s">
+        <v>120</v>
+      </c>
+      <c r="S3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>401</v>
+      </c>
+      <c r="B4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C4" t="s">
+        <v>394</v>
+      </c>
+      <c r="D4" t="s">
+        <v>403</v>
+      </c>
+      <c r="E4" t="s">
+        <v>404</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" t="b">
+        <v>1</v>
+      </c>
+      <c r="P4" t="s">
+        <v>120</v>
+      </c>
+      <c r="S4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>406</v>
+      </c>
+      <c r="B5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D5" t="s">
+        <v>408</v>
+      </c>
+      <c r="E5" t="s">
+        <v>409</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" t="s">
+        <v>120</v>
+      </c>
+      <c r="S5" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>410</v>
+      </c>
+      <c r="B6" t="s">
+        <v>411</v>
+      </c>
+      <c r="C6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D6" t="s">
+        <v>412</v>
+      </c>
+      <c r="E6" t="s">
+        <v>413</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O6" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" t="s">
+        <v>120</v>
+      </c>
+      <c r="S6" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>415</v>
+      </c>
+      <c r="B7" t="s">
+        <v>416</v>
+      </c>
+      <c r="C7" t="s">
+        <v>243</v>
+      </c>
+      <c r="D7" t="s">
+        <v>417</v>
+      </c>
+      <c r="E7" t="s">
+        <v>418</v>
+      </c>
+      <c r="K7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" t="s">
+        <v>28</v>
+      </c>
+      <c r="O7" t="b">
+        <v>1</v>
+      </c>
+      <c r="P7" t="s">
+        <v>120</v>
+      </c>
+      <c r="S7" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B8" t="s">
+        <v>420</v>
+      </c>
+      <c r="C8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D8" t="s">
+        <v>421</v>
+      </c>
+      <c r="E8" t="s">
+        <v>422</v>
+      </c>
+      <c r="K8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O8" t="b">
+        <v>1</v>
+      </c>
+      <c r="P8" t="s">
+        <v>120</v>
+      </c>
+      <c r="S8" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>424</v>
+      </c>
+      <c r="B9" t="s">
+        <v>425</v>
+      </c>
+      <c r="C9" t="s">
+        <v>243</v>
+      </c>
+      <c r="D9" t="s">
+        <v>426</v>
+      </c>
+      <c r="E9" t="s">
+        <v>427</v>
+      </c>
+      <c r="K9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O9" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" t="s">
+        <v>120</v>
+      </c>
+      <c r="S9" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>428</v>
+      </c>
+      <c r="B10" t="s">
+        <v>429</v>
+      </c>
+      <c r="C10" t="s">
+        <v>430</v>
+      </c>
+      <c r="D10" t="s">
+        <v>431</v>
+      </c>
+      <c r="E10" t="s">
+        <v>432</v>
+      </c>
+      <c r="K10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10" t="s">
+        <v>120</v>
+      </c>
+      <c r="S10" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>434</v>
+      </c>
+      <c r="B11" t="s">
+        <v>435</v>
+      </c>
+      <c r="C11" t="s">
+        <v>430</v>
+      </c>
+      <c r="D11" t="s">
+        <v>436</v>
+      </c>
+      <c r="E11" t="s">
+        <v>437</v>
+      </c>
+      <c r="K11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" t="s">
+        <v>28</v>
+      </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11" t="s">
+        <v>120</v>
+      </c>
+      <c r="S11" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>438</v>
+      </c>
+      <c r="B12" t="s">
+        <v>439</v>
+      </c>
+      <c r="C12" t="s">
+        <v>430</v>
+      </c>
+      <c r="D12" t="s">
+        <v>440</v>
+      </c>
+      <c r="E12" t="s">
+        <v>441</v>
+      </c>
+      <c r="K12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" t="s">
+        <v>28</v>
+      </c>
+      <c r="O12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P12" t="s">
+        <v>120</v>
+      </c>
+      <c r="S12" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>443</v>
+      </c>
+      <c r="B13" t="s">
+        <v>444</v>
+      </c>
+      <c r="C13" t="s">
+        <v>430</v>
+      </c>
+      <c r="D13" t="s">
+        <v>445</v>
+      </c>
+      <c r="E13" t="s">
+        <v>446</v>
+      </c>
+      <c r="K13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" t="s">
+        <v>28</v>
+      </c>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" t="s">
+        <v>120</v>
+      </c>
+      <c r="S13" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>447</v>
+      </c>
+      <c r="B14" t="s">
+        <v>448</v>
+      </c>
+      <c r="C14" t="s">
+        <v>243</v>
+      </c>
+      <c r="D14" t="s">
+        <v>449</v>
+      </c>
+      <c r="E14" t="s">
+        <v>450</v>
+      </c>
+      <c r="K14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" t="s">
+        <v>28</v>
+      </c>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" t="s">
+        <v>120</v>
+      </c>
+      <c r="S14" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>452</v>
+      </c>
+      <c r="B15" t="s">
+        <v>453</v>
+      </c>
+      <c r="C15" t="s">
+        <v>243</v>
+      </c>
+      <c r="D15" t="s">
+        <v>454</v>
+      </c>
+      <c r="E15" t="s">
+        <v>455</v>
+      </c>
+      <c r="K15" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" t="s">
+        <v>28</v>
+      </c>
+      <c r="O15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" t="s">
+        <v>120</v>
+      </c>
+      <c r="S15" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>457</v>
+      </c>
+      <c r="B16" t="s">
+        <v>458</v>
+      </c>
+      <c r="C16" t="s">
+        <v>459</v>
+      </c>
+      <c r="D16" t="s">
+        <v>460</v>
+      </c>
+      <c r="E16" t="s">
+        <v>461</v>
+      </c>
+      <c r="K16" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" t="s">
+        <v>28</v>
+      </c>
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16" t="s">
+        <v>120</v>
+      </c>
+      <c r="S16" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>463</v>
+      </c>
+      <c r="B17" t="s">
+        <v>464</v>
+      </c>
+      <c r="C17" t="s">
+        <v>459</v>
+      </c>
+      <c r="D17" t="s">
+        <v>465</v>
+      </c>
+      <c r="E17" t="s">
+        <v>466</v>
+      </c>
+      <c r="K17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O17" t="b">
+        <v>1</v>
+      </c>
+      <c r="P17" t="s">
+        <v>120</v>
+      </c>
+      <c r="S17" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>468</v>
+      </c>
+      <c r="B18" t="s">
+        <v>469</v>
+      </c>
+      <c r="C18" t="s">
+        <v>470</v>
+      </c>
+      <c r="D18" t="s">
+        <v>471</v>
+      </c>
+      <c r="E18" t="s">
+        <v>472</v>
+      </c>
+      <c r="K18" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" t="s">
+        <v>28</v>
+      </c>
+      <c r="O18" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" t="s">
+        <v>120</v>
+      </c>
+      <c r="S18" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>473</v>
+      </c>
+      <c r="B19" t="s">
+        <v>474</v>
+      </c>
+      <c r="C19" t="s">
+        <v>470</v>
+      </c>
+      <c r="D19" t="s">
+        <v>475</v>
+      </c>
+      <c r="E19" t="s">
+        <v>476</v>
+      </c>
+      <c r="K19" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" t="s">
+        <v>28</v>
+      </c>
+      <c r="O19" t="b">
+        <v>1</v>
+      </c>
+      <c r="P19" t="s">
+        <v>120</v>
+      </c>
+      <c r="S19" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>478</v>
+      </c>
+      <c r="B20" t="s">
+        <v>479</v>
+      </c>
+      <c r="C20" t="s">
+        <v>243</v>
+      </c>
+      <c r="D20" t="s">
+        <v>480</v>
+      </c>
+      <c r="E20" t="s">
+        <v>481</v>
+      </c>
+      <c r="K20" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" t="s">
+        <v>26</v>
+      </c>
+      <c r="M20" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" t="s">
+        <v>28</v>
+      </c>
+      <c r="O20" t="b">
+        <v>1</v>
+      </c>
+      <c r="P20" t="s">
+        <v>120</v>
+      </c>
+      <c r="S20" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>482</v>
+      </c>
+      <c r="B21" t="s">
+        <v>483</v>
+      </c>
+      <c r="C21" t="s">
+        <v>243</v>
+      </c>
+      <c r="D21" t="s">
+        <v>484</v>
+      </c>
+      <c r="E21" t="s">
+        <v>485</v>
+      </c>
+      <c r="K21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" t="s">
+        <v>28</v>
+      </c>
+      <c r="O21" t="b">
+        <v>1</v>
+      </c>
+      <c r="P21" t="s">
+        <v>120</v>
+      </c>
+      <c r="S21" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>486</v>
+      </c>
+      <c r="B22" t="s">
+        <v>487</v>
+      </c>
+      <c r="C22" t="s">
+        <v>243</v>
+      </c>
+      <c r="D22" t="s">
+        <v>488</v>
+      </c>
+      <c r="E22" t="s">
+        <v>446</v>
+      </c>
+      <c r="K22" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" t="s">
+        <v>26</v>
+      </c>
+      <c r="M22" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" t="s">
+        <v>28</v>
+      </c>
+      <c r="O22" t="b">
+        <v>1</v>
+      </c>
+      <c r="P22" t="s">
+        <v>120</v>
+      </c>
+      <c r="S22" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>489</v>
+      </c>
+      <c r="B23" t="s">
+        <v>490</v>
+      </c>
+      <c r="C23" t="s">
+        <v>243</v>
+      </c>
+      <c r="D23" t="s">
+        <v>491</v>
+      </c>
+      <c r="E23" t="s">
+        <v>492</v>
+      </c>
+      <c r="K23" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" t="s">
+        <v>28</v>
+      </c>
+      <c r="O23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P23" t="s">
+        <v>120</v>
+      </c>
+      <c r="S23" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>493</v>
+      </c>
+      <c r="B24" t="s">
+        <v>494</v>
+      </c>
+      <c r="C24" t="s">
+        <v>459</v>
+      </c>
+      <c r="D24" t="s">
+        <v>495</v>
+      </c>
+      <c r="E24" t="s">
+        <v>496</v>
+      </c>
+      <c r="K24" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" t="s">
+        <v>28</v>
+      </c>
+      <c r="O24" t="b">
+        <v>1</v>
+      </c>
+      <c r="P24" t="s">
+        <v>120</v>
+      </c>
+      <c r="S24" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>497</v>
+      </c>
+      <c r="B25" t="s">
+        <v>498</v>
+      </c>
+      <c r="C25" t="s">
+        <v>243</v>
+      </c>
+      <c r="D25" t="s">
+        <v>499</v>
+      </c>
+      <c r="E25" t="s">
+        <v>500</v>
+      </c>
+      <c r="K25" t="s">
+        <v>25</v>
+      </c>
+      <c r="L25" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" t="s">
+        <v>27</v>
+      </c>
+      <c r="N25" t="s">
+        <v>28</v>
+      </c>
+      <c r="O25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P25" t="s">
+        <v>120</v>
+      </c>
+      <c r="S25" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>501</v>
+      </c>
+      <c r="B26" t="s">
+        <v>502</v>
+      </c>
+      <c r="C26" t="s">
+        <v>470</v>
+      </c>
+      <c r="D26" t="s">
+        <v>503</v>
+      </c>
+      <c r="E26" t="s">
+        <v>504</v>
+      </c>
+      <c r="K26" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" t="s">
+        <v>28</v>
+      </c>
+      <c r="O26" t="b">
+        <v>1</v>
+      </c>
+      <c r="P26" t="s">
+        <v>120</v>
+      </c>
+      <c r="S26" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>505</v>
+      </c>
+      <c r="B27" t="s">
+        <v>506</v>
+      </c>
+      <c r="C27" t="s">
+        <v>470</v>
+      </c>
+      <c r="D27" t="s">
+        <v>507</v>
+      </c>
+      <c r="E27" t="s">
+        <v>508</v>
+      </c>
+      <c r="K27" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" t="s">
+        <v>27</v>
+      </c>
+      <c r="N27" t="s">
+        <v>28</v>
+      </c>
+      <c r="O27" t="b">
+        <v>1</v>
+      </c>
+      <c r="P27" t="s">
+        <v>120</v>
+      </c>
+      <c r="S27" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>509</v>
+      </c>
+      <c r="B28" t="s">
+        <v>510</v>
+      </c>
+      <c r="C28" t="s">
+        <v>243</v>
+      </c>
+      <c r="D28" t="s">
+        <v>511</v>
+      </c>
+      <c r="E28" t="s">
+        <v>512</v>
+      </c>
+      <c r="K28" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" t="s">
+        <v>26</v>
+      </c>
+      <c r="M28" t="s">
+        <v>27</v>
+      </c>
+      <c r="N28" t="s">
+        <v>28</v>
+      </c>
+      <c r="O28" t="b">
+        <v>1</v>
+      </c>
+      <c r="P28" t="s">
+        <v>120</v>
+      </c>
+      <c r="S28" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>513</v>
+      </c>
+      <c r="B29" t="s">
+        <v>514</v>
+      </c>
+      <c r="C29" t="s">
+        <v>243</v>
+      </c>
+      <c r="D29" t="s">
+        <v>515</v>
+      </c>
+      <c r="E29" t="s">
+        <v>455</v>
+      </c>
+      <c r="K29" t="s">
+        <v>25</v>
+      </c>
+      <c r="L29" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" t="s">
+        <v>27</v>
+      </c>
+      <c r="N29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O29" t="b">
+        <v>1</v>
+      </c>
+      <c r="P29" t="s">
+        <v>120</v>
+      </c>
+      <c r="S29" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>516</v>
+      </c>
+      <c r="B30" t="s">
+        <v>517</v>
+      </c>
+      <c r="C30" t="s">
+        <v>394</v>
+      </c>
+      <c r="D30" t="s">
+        <v>518</v>
+      </c>
+      <c r="E30" t="s">
+        <v>519</v>
+      </c>
+      <c r="K30" t="s">
+        <v>25</v>
+      </c>
+      <c r="L30" t="s">
+        <v>26</v>
+      </c>
+      <c r="M30" t="s">
+        <v>27</v>
+      </c>
+      <c r="N30" t="s">
+        <v>28</v>
+      </c>
+      <c r="O30" t="b">
+        <v>1</v>
+      </c>
+      <c r="P30" t="s">
+        <v>120</v>
+      </c>
+      <c r="S30" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>520</v>
+      </c>
+      <c r="B31" t="s">
+        <v>521</v>
+      </c>
+      <c r="C31" t="s">
+        <v>394</v>
+      </c>
+      <c r="D31" t="s">
+        <v>522</v>
+      </c>
+      <c r="E31" t="s">
+        <v>523</v>
+      </c>
+      <c r="K31" t="s">
+        <v>25</v>
+      </c>
+      <c r="L31" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" t="s">
+        <v>27</v>
+      </c>
+      <c r="N31" t="s">
+        <v>28</v>
+      </c>
+      <c r="O31" t="b">
+        <v>1</v>
+      </c>
+      <c r="P31" t="s">
+        <v>120</v>
+      </c>
+      <c r="S31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>524</v>
+      </c>
+      <c r="B32" t="s">
+        <v>525</v>
+      </c>
+      <c r="C32" t="s">
+        <v>394</v>
+      </c>
+      <c r="D32" t="s">
+        <v>526</v>
+      </c>
+      <c r="E32" t="s">
+        <v>527</v>
+      </c>
+      <c r="K32" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" t="s">
+        <v>26</v>
+      </c>
+      <c r="M32" t="s">
+        <v>27</v>
+      </c>
+      <c r="N32" t="s">
+        <v>28</v>
+      </c>
+      <c r="O32" t="b">
+        <v>1</v>
+      </c>
+      <c r="P32" t="s">
+        <v>120</v>
+      </c>
+      <c r="S32" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>528</v>
+      </c>
+      <c r="B33" t="s">
+        <v>529</v>
+      </c>
+      <c r="C33" t="s">
+        <v>394</v>
+      </c>
+      <c r="D33" t="s">
+        <v>530</v>
+      </c>
+      <c r="E33" t="s">
+        <v>531</v>
+      </c>
+      <c r="K33" t="s">
+        <v>25</v>
+      </c>
+      <c r="L33" t="s">
+        <v>26</v>
+      </c>
+      <c r="M33" t="s">
+        <v>27</v>
+      </c>
+      <c r="N33" t="s">
+        <v>28</v>
+      </c>
+      <c r="O33" t="b">
+        <v>1</v>
+      </c>
+      <c r="P33" t="s">
+        <v>120</v>
+      </c>
+      <c r="S33" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>532</v>
+      </c>
+      <c r="B34" t="s">
+        <v>533</v>
+      </c>
+      <c r="C34" t="s">
+        <v>394</v>
+      </c>
+      <c r="D34" t="s">
+        <v>534</v>
+      </c>
+      <c r="E34" t="s">
+        <v>461</v>
+      </c>
+      <c r="K34" t="s">
+        <v>25</v>
+      </c>
+      <c r="L34" t="s">
+        <v>26</v>
+      </c>
+      <c r="M34" t="s">
+        <v>27</v>
+      </c>
+      <c r="N34" t="s">
+        <v>28</v>
+      </c>
+      <c r="O34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P34" t="s">
+        <v>120</v>
+      </c>
+      <c r="S34" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>535</v>
+      </c>
+      <c r="B35" t="s">
+        <v>536</v>
+      </c>
+      <c r="C35" t="s">
+        <v>394</v>
+      </c>
+      <c r="D35" t="s">
+        <v>537</v>
+      </c>
+      <c r="E35" t="s">
+        <v>538</v>
+      </c>
+      <c r="K35" t="s">
+        <v>25</v>
+      </c>
+      <c r="L35" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" t="s">
+        <v>27</v>
+      </c>
+      <c r="N35" t="s">
+        <v>28</v>
+      </c>
+      <c r="O35" t="b">
+        <v>1</v>
+      </c>
+      <c r="P35" t="s">
+        <v>120</v>
+      </c>
+      <c r="S35" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>539</v>
+      </c>
+      <c r="B36" t="s">
+        <v>540</v>
+      </c>
+      <c r="C36" t="s">
+        <v>394</v>
+      </c>
+      <c r="D36" t="s">
+        <v>541</v>
+      </c>
+      <c r="E36" t="s">
+        <v>542</v>
+      </c>
+      <c r="K36" t="s">
+        <v>25</v>
+      </c>
+      <c r="L36" t="s">
+        <v>26</v>
+      </c>
+      <c r="M36" t="s">
+        <v>27</v>
+      </c>
+      <c r="N36" t="s">
+        <v>28</v>
+      </c>
+      <c r="O36" t="b">
+        <v>1</v>
+      </c>
+      <c r="P36" t="s">
+        <v>120</v>
+      </c>
+      <c r="S36" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>543</v>
+      </c>
+      <c r="B37" t="s">
+        <v>544</v>
+      </c>
+      <c r="C37" t="s">
+        <v>394</v>
+      </c>
+      <c r="D37" t="s">
+        <v>545</v>
+      </c>
+      <c r="E37" t="s">
+        <v>546</v>
+      </c>
+      <c r="K37" t="s">
+        <v>25</v>
+      </c>
+      <c r="L37" t="s">
+        <v>26</v>
+      </c>
+      <c r="M37" t="s">
+        <v>27</v>
+      </c>
+      <c r="N37" t="s">
+        <v>28</v>
+      </c>
+      <c r="O37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P37" t="s">
+        <v>120</v>
+      </c>
+      <c r="S37" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>547</v>
+      </c>
+      <c r="B38" t="s">
+        <v>548</v>
+      </c>
+      <c r="C38" t="s">
+        <v>394</v>
+      </c>
+      <c r="D38" t="s">
+        <v>549</v>
+      </c>
+      <c r="E38" t="s">
+        <v>550</v>
+      </c>
+      <c r="K38" t="s">
+        <v>25</v>
+      </c>
+      <c r="L38" t="s">
+        <v>26</v>
+      </c>
+      <c r="M38" t="s">
+        <v>27</v>
+      </c>
+      <c r="N38" t="s">
+        <v>28</v>
+      </c>
+      <c r="O38" t="b">
+        <v>1</v>
+      </c>
+      <c r="P38" t="s">
+        <v>120</v>
+      </c>
+      <c r="S38" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>551</v>
+      </c>
+      <c r="B39" t="s">
+        <v>552</v>
+      </c>
+      <c r="C39" t="s">
+        <v>394</v>
+      </c>
+      <c r="D39" t="s">
+        <v>553</v>
+      </c>
+      <c r="E39" t="s">
+        <v>466</v>
+      </c>
+      <c r="K39" t="s">
+        <v>25</v>
+      </c>
+      <c r="L39" t="s">
+        <v>26</v>
+      </c>
+      <c r="M39" t="s">
+        <v>27</v>
+      </c>
+      <c r="N39" t="s">
+        <v>28</v>
+      </c>
+      <c r="O39" t="b">
+        <v>1</v>
+      </c>
+      <c r="P39" t="s">
+        <v>120</v>
+      </c>
+      <c r="S39" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>554</v>
+      </c>
+      <c r="B40" t="s">
+        <v>555</v>
+      </c>
+      <c r="C40" t="s">
+        <v>430</v>
+      </c>
+      <c r="D40" t="s">
+        <v>556</v>
+      </c>
+      <c r="E40" t="s">
+        <v>557</v>
+      </c>
+      <c r="K40" t="s">
+        <v>25</v>
+      </c>
+      <c r="L40" t="s">
+        <v>26</v>
+      </c>
+      <c r="M40" t="s">
+        <v>27</v>
+      </c>
+      <c r="N40" t="s">
+        <v>28</v>
+      </c>
+      <c r="O40" t="b">
+        <v>1</v>
+      </c>
+      <c r="P40" t="s">
+        <v>120</v>
+      </c>
+      <c r="S40" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>558</v>
+      </c>
+      <c r="B41" t="s">
+        <v>559</v>
+      </c>
+      <c r="C41" t="s">
+        <v>430</v>
+      </c>
+      <c r="D41" t="s">
+        <v>560</v>
+      </c>
+      <c r="E41" t="s">
+        <v>561</v>
+      </c>
+      <c r="K41" t="s">
+        <v>25</v>
+      </c>
+      <c r="L41" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" t="s">
+        <v>27</v>
+      </c>
+      <c r="N41" t="s">
+        <v>28</v>
+      </c>
+      <c r="O41" t="b">
+        <v>1</v>
+      </c>
+      <c r="P41" t="s">
+        <v>120</v>
+      </c>
+      <c r="S41" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>562</v>
+      </c>
+      <c r="B42" t="s">
+        <v>563</v>
+      </c>
+      <c r="C42" t="s">
+        <v>430</v>
+      </c>
+      <c r="D42" t="s">
+        <v>564</v>
+      </c>
+      <c r="E42" t="s">
+        <v>565</v>
+      </c>
+      <c r="K42" t="s">
+        <v>25</v>
+      </c>
+      <c r="L42" t="s">
+        <v>26</v>
+      </c>
+      <c r="M42" t="s">
+        <v>27</v>
+      </c>
+      <c r="N42" t="s">
+        <v>28</v>
+      </c>
+      <c r="O42" t="b">
+        <v>1</v>
+      </c>
+      <c r="P42" t="s">
+        <v>120</v>
+      </c>
+      <c r="S42" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>566</v>
+      </c>
+      <c r="B43" t="s">
+        <v>567</v>
+      </c>
+      <c r="C43" t="s">
+        <v>430</v>
+      </c>
+      <c r="D43" t="s">
+        <v>568</v>
+      </c>
+      <c r="E43" t="s">
+        <v>569</v>
+      </c>
+      <c r="K43" t="s">
+        <v>25</v>
+      </c>
+      <c r="L43" t="s">
+        <v>26</v>
+      </c>
+      <c r="M43" t="s">
+        <v>27</v>
+      </c>
+      <c r="N43" t="s">
+        <v>28</v>
+      </c>
+      <c r="O43" t="b">
+        <v>1</v>
+      </c>
+      <c r="P43" t="s">
+        <v>120</v>
+      </c>
+      <c r="S43" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>570</v>
+      </c>
+      <c r="B44" t="s">
+        <v>571</v>
+      </c>
+      <c r="C44" t="s">
+        <v>430</v>
+      </c>
+      <c r="D44" t="s">
+        <v>572</v>
+      </c>
+      <c r="E44" t="s">
+        <v>573</v>
+      </c>
+      <c r="K44" t="s">
+        <v>25</v>
+      </c>
+      <c r="L44" t="s">
+        <v>26</v>
+      </c>
+      <c r="M44" t="s">
+        <v>27</v>
+      </c>
+      <c r="N44" t="s">
+        <v>28</v>
+      </c>
+      <c r="O44" t="b">
+        <v>1</v>
+      </c>
+      <c r="P44" t="s">
+        <v>120</v>
+      </c>
+      <c r="S44" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>574</v>
+      </c>
+      <c r="B45" t="s">
+        <v>575</v>
+      </c>
+      <c r="C45" t="s">
+        <v>430</v>
+      </c>
+      <c r="D45" t="s">
+        <v>576</v>
+      </c>
+      <c r="E45" t="s">
+        <v>577</v>
+      </c>
+      <c r="K45" t="s">
+        <v>25</v>
+      </c>
+      <c r="L45" t="s">
+        <v>26</v>
+      </c>
+      <c r="M45" t="s">
+        <v>27</v>
+      </c>
+      <c r="N45" t="s">
+        <v>28</v>
+      </c>
+      <c r="O45" t="b">
+        <v>1</v>
+      </c>
+      <c r="P45" t="s">
+        <v>120</v>
+      </c>
+      <c r="S45" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>578</v>
+      </c>
+      <c r="B46" t="s">
+        <v>579</v>
+      </c>
+      <c r="C46" t="s">
+        <v>430</v>
+      </c>
+      <c r="D46" t="s">
+        <v>580</v>
+      </c>
+      <c r="E46" t="s">
+        <v>581</v>
+      </c>
+      <c r="K46" t="s">
+        <v>25</v>
+      </c>
+      <c r="L46" t="s">
+        <v>26</v>
+      </c>
+      <c r="M46" t="s">
+        <v>27</v>
+      </c>
+      <c r="N46" t="s">
+        <v>28</v>
+      </c>
+      <c r="O46" t="b">
+        <v>1</v>
+      </c>
+      <c r="P46" t="s">
+        <v>120</v>
+      </c>
+      <c r="S46" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>582</v>
+      </c>
+      <c r="B47" t="s">
+        <v>583</v>
+      </c>
+      <c r="C47" t="s">
+        <v>430</v>
+      </c>
+      <c r="D47" t="s">
+        <v>584</v>
+      </c>
+      <c r="E47" t="s">
+        <v>585</v>
+      </c>
+      <c r="K47" t="s">
+        <v>25</v>
+      </c>
+      <c r="L47" t="s">
+        <v>26</v>
+      </c>
+      <c r="M47" t="s">
+        <v>27</v>
+      </c>
+      <c r="N47" t="s">
+        <v>28</v>
+      </c>
+      <c r="O47" t="b">
+        <v>1</v>
+      </c>
+      <c r="P47" t="s">
+        <v>120</v>
+      </c>
+      <c r="S47" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>586</v>
+      </c>
+      <c r="B48" t="s">
+        <v>587</v>
+      </c>
+      <c r="C48" t="s">
+        <v>430</v>
+      </c>
+      <c r="D48" t="s">
+        <v>588</v>
+      </c>
+      <c r="E48" t="s">
+        <v>589</v>
+      </c>
+      <c r="K48" t="s">
+        <v>25</v>
+      </c>
+      <c r="L48" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" t="s">
+        <v>27</v>
+      </c>
+      <c r="N48" t="s">
+        <v>28</v>
+      </c>
+      <c r="O48" t="b">
+        <v>1</v>
+      </c>
+      <c r="P48" t="s">
+        <v>120</v>
+      </c>
+      <c r="S48" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>590</v>
+      </c>
+      <c r="B49" t="s">
+        <v>591</v>
+      </c>
+      <c r="C49" t="s">
+        <v>430</v>
+      </c>
+      <c r="D49" t="s">
+        <v>592</v>
+      </c>
+      <c r="E49" t="s">
+        <v>593</v>
+      </c>
+      <c r="K49" t="s">
+        <v>25</v>
+      </c>
+      <c r="L49" t="s">
+        <v>26</v>
+      </c>
+      <c r="M49" t="s">
+        <v>27</v>
+      </c>
+      <c r="N49" t="s">
+        <v>28</v>
+      </c>
+      <c r="O49" t="b">
+        <v>1</v>
+      </c>
+      <c r="P49" t="s">
+        <v>120</v>
+      </c>
+      <c r="S49" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>594</v>
+      </c>
+      <c r="B50" t="s">
+        <v>595</v>
+      </c>
+      <c r="C50" t="s">
+        <v>430</v>
+      </c>
+      <c r="D50" t="s">
+        <v>596</v>
+      </c>
+      <c r="E50" t="s">
+        <v>597</v>
+      </c>
+      <c r="K50" t="s">
+        <v>25</v>
+      </c>
+      <c r="L50" t="s">
+        <v>26</v>
+      </c>
+      <c r="M50" t="s">
+        <v>27</v>
+      </c>
+      <c r="N50" t="s">
+        <v>28</v>
+      </c>
+      <c r="O50" t="b">
+        <v>1</v>
+      </c>
+      <c r="P50" t="s">
+        <v>120</v>
+      </c>
+      <c r="S50" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>598</v>
+      </c>
+      <c r="B51" t="s">
+        <v>599</v>
+      </c>
+      <c r="C51" t="s">
+        <v>430</v>
+      </c>
+      <c r="D51" t="s">
+        <v>600</v>
+      </c>
+      <c r="E51" t="s">
+        <v>601</v>
+      </c>
+      <c r="K51" t="s">
+        <v>25</v>
+      </c>
+      <c r="L51" t="s">
+        <v>26</v>
+      </c>
+      <c r="M51" t="s">
+        <v>27</v>
+      </c>
+      <c r="N51" t="s">
+        <v>28</v>
+      </c>
+      <c r="O51" t="b">
+        <v>1</v>
+      </c>
+      <c r="P51" t="s">
+        <v>120</v>
+      </c>
+      <c r="S51" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>602</v>
+      </c>
+      <c r="B52" t="s">
+        <v>603</v>
+      </c>
+      <c r="C52" t="s">
+        <v>430</v>
+      </c>
+      <c r="D52" t="s">
+        <v>604</v>
+      </c>
+      <c r="E52" t="s">
+        <v>605</v>
+      </c>
+      <c r="K52" t="s">
+        <v>25</v>
+      </c>
+      <c r="L52" t="s">
+        <v>26</v>
+      </c>
+      <c r="M52" t="s">
+        <v>27</v>
+      </c>
+      <c r="N52" t="s">
+        <v>28</v>
+      </c>
+      <c r="O52" t="b">
+        <v>1</v>
+      </c>
+      <c r="P52" t="s">
+        <v>120</v>
+      </c>
+      <c r="S52" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>606</v>
+      </c>
+      <c r="B53" t="s">
+        <v>607</v>
+      </c>
+      <c r="C53" t="s">
+        <v>430</v>
+      </c>
+      <c r="D53" t="s">
+        <v>608</v>
+      </c>
+      <c r="E53" t="s">
+        <v>609</v>
+      </c>
+      <c r="K53" t="s">
+        <v>25</v>
+      </c>
+      <c r="L53" t="s">
+        <v>26</v>
+      </c>
+      <c r="M53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N53" t="s">
+        <v>28</v>
+      </c>
+      <c r="O53" t="b">
+        <v>1</v>
+      </c>
+      <c r="P53" t="s">
+        <v>120</v>
+      </c>
+      <c r="S53" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>610</v>
+      </c>
+      <c r="B54" t="s">
+        <v>611</v>
+      </c>
+      <c r="C54" t="s">
+        <v>430</v>
+      </c>
+      <c r="D54" t="s">
+        <v>612</v>
+      </c>
+      <c r="E54" t="s">
+        <v>613</v>
+      </c>
+      <c r="K54" t="s">
+        <v>25</v>
+      </c>
+      <c r="L54" t="s">
+        <v>26</v>
+      </c>
+      <c r="M54" t="s">
+        <v>27</v>
+      </c>
+      <c r="N54" t="s">
+        <v>28</v>
+      </c>
+      <c r="O54" t="b">
+        <v>1</v>
+      </c>
+      <c r="P54" t="s">
+        <v>120</v>
+      </c>
+      <c r="S54" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>614</v>
+      </c>
+      <c r="B55" t="s">
+        <v>615</v>
+      </c>
+      <c r="C55" t="s">
+        <v>430</v>
+      </c>
+      <c r="D55" t="s">
+        <v>616</v>
+      </c>
+      <c r="E55" t="s">
+        <v>617</v>
+      </c>
+      <c r="K55" t="s">
+        <v>25</v>
+      </c>
+      <c r="L55" t="s">
+        <v>26</v>
+      </c>
+      <c r="M55" t="s">
+        <v>27</v>
+      </c>
+      <c r="N55" t="s">
+        <v>28</v>
+      </c>
+      <c r="O55" t="b">
+        <v>1</v>
+      </c>
+      <c r="P55" t="s">
+        <v>120</v>
+      </c>
+      <c r="S55" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>618</v>
+      </c>
+      <c r="B56" t="s">
+        <v>619</v>
+      </c>
+      <c r="C56" t="s">
+        <v>430</v>
+      </c>
+      <c r="D56" t="s">
+        <v>620</v>
+      </c>
+      <c r="E56" t="s">
+        <v>621</v>
+      </c>
+      <c r="K56" t="s">
+        <v>25</v>
+      </c>
+      <c r="L56" t="s">
+        <v>26</v>
+      </c>
+      <c r="M56" t="s">
+        <v>27</v>
+      </c>
+      <c r="N56" t="s">
+        <v>28</v>
+      </c>
+      <c r="O56" t="b">
+        <v>1</v>
+      </c>
+      <c r="P56" t="s">
+        <v>120</v>
+      </c>
+      <c r="S56" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>622</v>
+      </c>
+      <c r="B57" t="s">
+        <v>623</v>
+      </c>
+      <c r="C57" t="s">
+        <v>243</v>
+      </c>
+      <c r="D57" t="s">
+        <v>624</v>
+      </c>
+      <c r="E57" t="s">
+        <v>472</v>
+      </c>
+      <c r="K57" t="s">
+        <v>25</v>
+      </c>
+      <c r="L57" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" t="s">
+        <v>27</v>
+      </c>
+      <c r="N57" t="s">
+        <v>28</v>
+      </c>
+      <c r="O57" t="b">
+        <v>1</v>
+      </c>
+      <c r="P57" t="s">
+        <v>120</v>
+      </c>
+      <c r="S57" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>625</v>
+      </c>
+      <c r="B58" t="s">
+        <v>626</v>
+      </c>
+      <c r="C58" t="s">
+        <v>430</v>
+      </c>
+      <c r="D58" t="s">
+        <v>627</v>
+      </c>
+      <c r="E58" t="s">
+        <v>628</v>
+      </c>
+      <c r="K58" t="s">
+        <v>25</v>
+      </c>
+      <c r="L58" t="s">
+        <v>26</v>
+      </c>
+      <c r="M58" t="s">
+        <v>27</v>
+      </c>
+      <c r="N58" t="s">
+        <v>28</v>
+      </c>
+      <c r="O58" t="b">
+        <v>1</v>
+      </c>
+      <c r="P58" t="s">
+        <v>120</v>
+      </c>
+      <c r="S58" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>629</v>
+      </c>
+      <c r="B59" t="s">
+        <v>630</v>
+      </c>
+      <c r="C59" t="s">
+        <v>430</v>
+      </c>
+      <c r="D59" t="s">
+        <v>631</v>
+      </c>
+      <c r="E59" t="s">
+        <v>476</v>
+      </c>
+      <c r="K59" t="s">
+        <v>25</v>
+      </c>
+      <c r="L59" t="s">
+        <v>26</v>
+      </c>
+      <c r="M59" t="s">
+        <v>27</v>
+      </c>
+      <c r="N59" t="s">
+        <v>28</v>
+      </c>
+      <c r="O59" t="b">
+        <v>1</v>
+      </c>
+      <c r="P59" t="s">
+        <v>120</v>
+      </c>
+      <c r="S59" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>632</v>
+      </c>
+      <c r="B60" t="s">
+        <v>633</v>
+      </c>
+      <c r="C60" t="s">
+        <v>430</v>
+      </c>
+      <c r="D60" t="s">
+        <v>634</v>
+      </c>
+      <c r="E60" t="s">
+        <v>635</v>
+      </c>
+      <c r="K60" t="s">
+        <v>25</v>
+      </c>
+      <c r="L60" t="s">
+        <v>26</v>
+      </c>
+      <c r="M60" t="s">
+        <v>27</v>
+      </c>
+      <c r="N60" t="s">
+        <v>28</v>
+      </c>
+      <c r="O60" t="b">
+        <v>1</v>
+      </c>
+      <c r="P60" t="s">
+        <v>120</v>
+      </c>
+      <c r="S60" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>636</v>
+      </c>
+      <c r="B61" t="s">
+        <v>637</v>
+      </c>
+      <c r="C61" t="s">
+        <v>430</v>
+      </c>
+      <c r="D61" t="s">
+        <v>638</v>
+      </c>
+      <c r="E61" t="s">
+        <v>639</v>
+      </c>
+      <c r="K61" t="s">
+        <v>25</v>
+      </c>
+      <c r="L61" t="s">
+        <v>26</v>
+      </c>
+      <c r="M61" t="s">
+        <v>27</v>
+      </c>
+      <c r="N61" t="s">
+        <v>28</v>
+      </c>
+      <c r="O61" t="b">
+        <v>1</v>
+      </c>
+      <c r="P61" t="s">
+        <v>120</v>
+      </c>
+      <c r="S61" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>640</v>
+      </c>
+      <c r="B62" t="s">
+        <v>641</v>
+      </c>
+      <c r="C62" t="s">
+        <v>430</v>
+      </c>
+      <c r="D62" t="s">
+        <v>642</v>
+      </c>
+      <c r="E62" t="s">
+        <v>643</v>
+      </c>
+      <c r="K62" t="s">
+        <v>25</v>
+      </c>
+      <c r="L62" t="s">
+        <v>26</v>
+      </c>
+      <c r="M62" t="s">
+        <v>27</v>
+      </c>
+      <c r="N62" t="s">
+        <v>28</v>
+      </c>
+      <c r="O62" t="b">
+        <v>1</v>
+      </c>
+      <c r="P62" t="s">
+        <v>120</v>
+      </c>
+      <c r="S62" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>644</v>
+      </c>
+      <c r="B63" t="s">
+        <v>645</v>
+      </c>
+      <c r="C63" t="s">
+        <v>243</v>
+      </c>
+      <c r="D63" t="s">
+        <v>646</v>
+      </c>
+      <c r="E63" t="s">
+        <v>481</v>
+      </c>
+      <c r="K63" t="s">
+        <v>25</v>
+      </c>
+      <c r="L63" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" t="s">
+        <v>27</v>
+      </c>
+      <c r="N63" t="s">
+        <v>28</v>
+      </c>
+      <c r="O63" t="b">
+        <v>1</v>
+      </c>
+      <c r="P63" t="s">
+        <v>120</v>
+      </c>
+      <c r="S63" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>647</v>
+      </c>
+      <c r="B64" t="s">
+        <v>648</v>
+      </c>
+      <c r="C64" t="s">
+        <v>243</v>
+      </c>
+      <c r="D64" t="s">
+        <v>649</v>
+      </c>
+      <c r="E64" t="s">
+        <v>650</v>
+      </c>
+      <c r="K64" t="s">
+        <v>25</v>
+      </c>
+      <c r="L64" t="s">
+        <v>26</v>
+      </c>
+      <c r="M64" t="s">
+        <v>27</v>
+      </c>
+      <c r="N64" t="s">
+        <v>28</v>
+      </c>
+      <c r="O64" t="b">
+        <v>1</v>
+      </c>
+      <c r="P64" t="s">
+        <v>120</v>
+      </c>
+      <c r="S64" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>651</v>
+      </c>
+      <c r="B65" t="s">
+        <v>652</v>
+      </c>
+      <c r="C65" t="s">
+        <v>243</v>
+      </c>
+      <c r="D65" t="s">
+        <v>653</v>
+      </c>
+      <c r="E65" t="s">
+        <v>654</v>
+      </c>
+      <c r="K65" t="s">
+        <v>25</v>
+      </c>
+      <c r="L65" t="s">
+        <v>26</v>
+      </c>
+      <c r="M65" t="s">
+        <v>27</v>
+      </c>
+      <c r="N65" t="s">
+        <v>28</v>
+      </c>
+      <c r="O65" t="b">
+        <v>1</v>
+      </c>
+      <c r="P65" t="s">
+        <v>120</v>
+      </c>
+      <c r="S65" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>655</v>
+      </c>
+      <c r="B66" t="s">
+        <v>656</v>
+      </c>
+      <c r="C66" t="s">
+        <v>243</v>
+      </c>
+      <c r="D66" t="s">
+        <v>657</v>
+      </c>
+      <c r="E66" t="s">
+        <v>485</v>
+      </c>
+      <c r="K66" t="s">
+        <v>25</v>
+      </c>
+      <c r="L66" t="s">
+        <v>26</v>
+      </c>
+      <c r="M66" t="s">
+        <v>27</v>
+      </c>
+      <c r="N66" t="s">
+        <v>28</v>
+      </c>
+      <c r="O66" t="b">
+        <v>1</v>
+      </c>
+      <c r="P66" t="s">
+        <v>120</v>
+      </c>
+      <c r="S66" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>658</v>
+      </c>
+      <c r="B67" t="s">
+        <v>659</v>
+      </c>
+      <c r="C67" t="s">
+        <v>243</v>
+      </c>
+      <c r="D67" t="s">
+        <v>660</v>
+      </c>
+      <c r="E67" t="s">
+        <v>661</v>
+      </c>
+      <c r="K67" t="s">
+        <v>25</v>
+      </c>
+      <c r="L67" t="s">
+        <v>26</v>
+      </c>
+      <c r="M67" t="s">
+        <v>27</v>
+      </c>
+      <c r="N67" t="s">
+        <v>28</v>
+      </c>
+      <c r="O67" t="b">
+        <v>1</v>
+      </c>
+      <c r="P67" t="s">
+        <v>120</v>
+      </c>
+      <c r="S67" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>662</v>
+      </c>
+      <c r="B68" t="s">
+        <v>663</v>
+      </c>
+      <c r="C68" t="s">
+        <v>243</v>
+      </c>
+      <c r="D68" t="s">
+        <v>664</v>
+      </c>
+      <c r="E68" t="s">
+        <v>665</v>
+      </c>
+      <c r="K68" t="s">
+        <v>25</v>
+      </c>
+      <c r="L68" t="s">
+        <v>26</v>
+      </c>
+      <c r="M68" t="s">
+        <v>27</v>
+      </c>
+      <c r="N68" t="s">
+        <v>28</v>
+      </c>
+      <c r="O68" t="b">
+        <v>1</v>
+      </c>
+      <c r="P68" t="s">
+        <v>120</v>
+      </c>
+      <c r="S68" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>666</v>
+      </c>
+      <c r="B69" t="s">
+        <v>667</v>
+      </c>
+      <c r="C69" t="s">
+        <v>243</v>
+      </c>
+      <c r="D69" t="s">
+        <v>668</v>
+      </c>
+      <c r="E69" t="s">
+        <v>669</v>
+      </c>
+      <c r="K69" t="s">
+        <v>25</v>
+      </c>
+      <c r="L69" t="s">
+        <v>26</v>
+      </c>
+      <c r="M69" t="s">
+        <v>27</v>
+      </c>
+      <c r="N69" t="s">
+        <v>28</v>
+      </c>
+      <c r="O69" t="b">
+        <v>1</v>
+      </c>
+      <c r="P69" t="s">
+        <v>120</v>
+      </c>
+      <c r="S69" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>670</v>
+      </c>
+      <c r="B70" t="s">
+        <v>671</v>
+      </c>
+      <c r="C70" t="s">
+        <v>243</v>
+      </c>
+      <c r="D70" t="s">
+        <v>672</v>
+      </c>
+      <c r="E70" t="s">
+        <v>673</v>
+      </c>
+      <c r="K70" t="s">
+        <v>25</v>
+      </c>
+      <c r="L70" t="s">
+        <v>26</v>
+      </c>
+      <c r="M70" t="s">
+        <v>27</v>
+      </c>
+      <c r="N70" t="s">
+        <v>28</v>
+      </c>
+      <c r="O70" t="b">
+        <v>1</v>
+      </c>
+      <c r="P70" t="s">
+        <v>120</v>
+      </c>
+      <c r="S70" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>674</v>
+      </c>
+      <c r="B71" t="s">
+        <v>675</v>
+      </c>
+      <c r="C71" t="s">
+        <v>243</v>
+      </c>
+      <c r="D71" t="s">
+        <v>676</v>
+      </c>
+      <c r="E71" t="s">
+        <v>677</v>
+      </c>
+      <c r="K71" t="s">
+        <v>25</v>
+      </c>
+      <c r="L71" t="s">
+        <v>26</v>
+      </c>
+      <c r="M71" t="s">
+        <v>27</v>
+      </c>
+      <c r="N71" t="s">
+        <v>28</v>
+      </c>
+      <c r="O71" t="b">
+        <v>1</v>
+      </c>
+      <c r="P71" t="s">
+        <v>120</v>
+      </c>
+      <c r="S71" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>678</v>
+      </c>
+      <c r="B72" t="s">
+        <v>679</v>
+      </c>
+      <c r="C72" t="s">
+        <v>243</v>
+      </c>
+      <c r="D72" t="s">
+        <v>680</v>
+      </c>
+      <c r="E72" t="s">
+        <v>681</v>
+      </c>
+      <c r="K72" t="s">
+        <v>25</v>
+      </c>
+      <c r="L72" t="s">
+        <v>26</v>
+      </c>
+      <c r="M72" t="s">
+        <v>27</v>
+      </c>
+      <c r="N72" t="s">
+        <v>28</v>
+      </c>
+      <c r="O72" t="b">
+        <v>1</v>
+      </c>
+      <c r="P72" t="s">
+        <v>120</v>
+      </c>
+      <c r="S72" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>682</v>
+      </c>
+      <c r="B73" t="s">
+        <v>683</v>
+      </c>
+      <c r="C73" t="s">
+        <v>243</v>
+      </c>
+      <c r="D73" t="s">
+        <v>684</v>
+      </c>
+      <c r="E73" t="s">
+        <v>685</v>
+      </c>
+      <c r="K73" t="s">
+        <v>25</v>
+      </c>
+      <c r="L73" t="s">
+        <v>26</v>
+      </c>
+      <c r="M73" t="s">
+        <v>27</v>
+      </c>
+      <c r="N73" t="s">
+        <v>28</v>
+      </c>
+      <c r="O73" t="b">
+        <v>1</v>
+      </c>
+      <c r="P73" t="s">
+        <v>120</v>
+      </c>
+      <c r="S73" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>686</v>
+      </c>
+      <c r="B74" t="s">
+        <v>687</v>
+      </c>
+      <c r="C74" t="s">
+        <v>243</v>
+      </c>
+      <c r="D74" t="s">
+        <v>688</v>
+      </c>
+      <c r="E74" t="s">
+        <v>689</v>
+      </c>
+      <c r="K74" t="s">
+        <v>25</v>
+      </c>
+      <c r="L74" t="s">
+        <v>26</v>
+      </c>
+      <c r="M74" t="s">
+        <v>27</v>
+      </c>
+      <c r="N74" t="s">
+        <v>28</v>
+      </c>
+      <c r="O74" t="b">
+        <v>1</v>
+      </c>
+      <c r="P74" t="s">
+        <v>120</v>
+      </c>
+      <c r="S74" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>690</v>
+      </c>
+      <c r="B75" t="s">
+        <v>691</v>
+      </c>
+      <c r="C75" t="s">
+        <v>243</v>
+      </c>
+      <c r="D75" t="s">
+        <v>692</v>
+      </c>
+      <c r="E75" t="s">
+        <v>693</v>
+      </c>
+      <c r="K75" t="s">
+        <v>25</v>
+      </c>
+      <c r="L75" t="s">
+        <v>26</v>
+      </c>
+      <c r="M75" t="s">
+        <v>27</v>
+      </c>
+      <c r="N75" t="s">
+        <v>28</v>
+      </c>
+      <c r="O75" t="b">
+        <v>1</v>
+      </c>
+      <c r="P75" t="s">
+        <v>120</v>
+      </c>
+      <c r="S75" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>694</v>
+      </c>
+      <c r="B76" t="s">
+        <v>695</v>
+      </c>
+      <c r="C76" t="s">
+        <v>243</v>
+      </c>
+      <c r="D76" t="s">
+        <v>696</v>
+      </c>
+      <c r="E76" t="s">
+        <v>697</v>
+      </c>
+      <c r="K76" t="s">
+        <v>25</v>
+      </c>
+      <c r="L76" t="s">
+        <v>26</v>
+      </c>
+      <c r="M76" t="s">
+        <v>27</v>
+      </c>
+      <c r="N76" t="s">
+        <v>28</v>
+      </c>
+      <c r="O76" t="b">
+        <v>1</v>
+      </c>
+      <c r="P76" t="s">
+        <v>120</v>
+      </c>
+      <c r="S76" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>698</v>
+      </c>
+      <c r="B77" t="s">
+        <v>699</v>
+      </c>
+      <c r="C77" t="s">
+        <v>243</v>
+      </c>
+      <c r="D77" t="s">
+        <v>700</v>
+      </c>
+      <c r="E77" t="s">
+        <v>701</v>
+      </c>
+      <c r="K77" t="s">
+        <v>25</v>
+      </c>
+      <c r="L77" t="s">
+        <v>26</v>
+      </c>
+      <c r="M77" t="s">
+        <v>27</v>
+      </c>
+      <c r="N77" t="s">
+        <v>28</v>
+      </c>
+      <c r="O77" t="b">
+        <v>1</v>
+      </c>
+      <c r="P77" t="s">
+        <v>120</v>
+      </c>
+      <c r="S77" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>702</v>
+      </c>
+      <c r="B78" t="s">
+        <v>703</v>
+      </c>
+      <c r="C78" t="s">
+        <v>243</v>
+      </c>
+      <c r="D78" t="s">
+        <v>704</v>
+      </c>
+      <c r="E78" t="s">
+        <v>705</v>
+      </c>
+      <c r="K78" t="s">
+        <v>25</v>
+      </c>
+      <c r="L78" t="s">
+        <v>26</v>
+      </c>
+      <c r="M78" t="s">
+        <v>27</v>
+      </c>
+      <c r="N78" t="s">
+        <v>28</v>
+      </c>
+      <c r="O78" t="b">
+        <v>1</v>
+      </c>
+      <c r="P78" t="s">
+        <v>120</v>
+      </c>
+      <c r="S78" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>706</v>
+      </c>
+      <c r="B79" t="s">
+        <v>707</v>
+      </c>
+      <c r="C79" t="s">
+        <v>243</v>
+      </c>
+      <c r="D79" t="s">
+        <v>708</v>
+      </c>
+      <c r="E79" t="s">
+        <v>709</v>
+      </c>
+      <c r="K79" t="s">
+        <v>25</v>
+      </c>
+      <c r="L79" t="s">
+        <v>26</v>
+      </c>
+      <c r="M79" t="s">
+        <v>27</v>
+      </c>
+      <c r="N79" t="s">
+        <v>28</v>
+      </c>
+      <c r="O79" t="b">
+        <v>1</v>
+      </c>
+      <c r="P79" t="s">
+        <v>120</v>
+      </c>
+      <c r="S79" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>710</v>
+      </c>
+      <c r="B80" t="s">
+        <v>711</v>
+      </c>
+      <c r="C80" t="s">
+        <v>243</v>
+      </c>
+      <c r="D80" t="s">
+        <v>712</v>
+      </c>
+      <c r="E80" t="s">
+        <v>713</v>
+      </c>
+      <c r="K80" t="s">
+        <v>25</v>
+      </c>
+      <c r="L80" t="s">
+        <v>26</v>
+      </c>
+      <c r="M80" t="s">
+        <v>27</v>
+      </c>
+      <c r="N80" t="s">
+        <v>28</v>
+      </c>
+      <c r="O80" t="b">
+        <v>1</v>
+      </c>
+      <c r="P80" t="s">
+        <v>120</v>
+      </c>
+      <c r="S80" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>714</v>
+      </c>
+      <c r="B81" t="s">
+        <v>715</v>
+      </c>
+      <c r="C81" t="s">
+        <v>243</v>
+      </c>
+      <c r="D81" t="s">
+        <v>716</v>
+      </c>
+      <c r="E81" t="s">
+        <v>717</v>
+      </c>
+      <c r="K81" t="s">
+        <v>25</v>
+      </c>
+      <c r="L81" t="s">
+        <v>26</v>
+      </c>
+      <c r="M81" t="s">
+        <v>27</v>
+      </c>
+      <c r="N81" t="s">
+        <v>28</v>
+      </c>
+      <c r="O81" t="b">
+        <v>1</v>
+      </c>
+      <c r="P81" t="s">
+        <v>120</v>
+      </c>
+      <c r="S81" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>718</v>
+      </c>
+      <c r="B82" t="s">
+        <v>719</v>
+      </c>
+      <c r="C82" t="s">
+        <v>243</v>
+      </c>
+      <c r="D82" t="s">
+        <v>720</v>
+      </c>
+      <c r="E82" t="s">
+        <v>721</v>
+      </c>
+      <c r="K82" t="s">
+        <v>25</v>
+      </c>
+      <c r="L82" t="s">
+        <v>26</v>
+      </c>
+      <c r="M82" t="s">
+        <v>27</v>
+      </c>
+      <c r="N82" t="s">
+        <v>28</v>
+      </c>
+      <c r="O82" t="b">
+        <v>1</v>
+      </c>
+      <c r="P82" t="s">
+        <v>120</v>
+      </c>
+      <c r="S82" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>722</v>
+      </c>
+      <c r="B83" t="s">
+        <v>723</v>
+      </c>
+      <c r="C83" t="s">
+        <v>243</v>
+      </c>
+      <c r="D83" t="s">
+        <v>724</v>
+      </c>
+      <c r="E83" t="s">
+        <v>725</v>
+      </c>
+      <c r="K83" t="s">
+        <v>25</v>
+      </c>
+      <c r="L83" t="s">
+        <v>26</v>
+      </c>
+      <c r="M83" t="s">
+        <v>27</v>
+      </c>
+      <c r="N83" t="s">
+        <v>28</v>
+      </c>
+      <c r="O83" t="b">
+        <v>1</v>
+      </c>
+      <c r="P83" t="s">
+        <v>120</v>
+      </c>
+      <c r="S83" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>726</v>
+      </c>
+      <c r="B84" t="s">
+        <v>727</v>
+      </c>
+      <c r="C84" t="s">
+        <v>243</v>
+      </c>
+      <c r="D84" t="s">
+        <v>728</v>
+      </c>
+      <c r="E84" t="s">
+        <v>729</v>
+      </c>
+      <c r="K84" t="s">
+        <v>25</v>
+      </c>
+      <c r="L84" t="s">
+        <v>26</v>
+      </c>
+      <c r="M84" t="s">
+        <v>27</v>
+      </c>
+      <c r="N84" t="s">
+        <v>28</v>
+      </c>
+      <c r="O84" t="b">
+        <v>1</v>
+      </c>
+      <c r="P84" t="s">
+        <v>120</v>
+      </c>
+      <c r="S84" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>730</v>
+      </c>
+      <c r="B85" t="s">
+        <v>731</v>
+      </c>
+      <c r="C85" t="s">
+        <v>243</v>
+      </c>
+      <c r="D85" t="s">
+        <v>732</v>
+      </c>
+      <c r="E85" t="s">
+        <v>733</v>
+      </c>
+      <c r="K85" t="s">
+        <v>25</v>
+      </c>
+      <c r="L85" t="s">
+        <v>26</v>
+      </c>
+      <c r="M85" t="s">
+        <v>27</v>
+      </c>
+      <c r="N85" t="s">
+        <v>28</v>
+      </c>
+      <c r="O85" t="b">
+        <v>1</v>
+      </c>
+      <c r="P85" t="s">
+        <v>120</v>
+      </c>
+      <c r="S85" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>734</v>
+      </c>
+      <c r="B86" t="s">
+        <v>735</v>
+      </c>
+      <c r="C86" t="s">
+        <v>243</v>
+      </c>
+      <c r="D86" t="s">
+        <v>736</v>
+      </c>
+      <c r="E86" t="s">
+        <v>737</v>
+      </c>
+      <c r="K86" t="s">
+        <v>25</v>
+      </c>
+      <c r="L86" t="s">
+        <v>26</v>
+      </c>
+      <c r="M86" t="s">
+        <v>27</v>
+      </c>
+      <c r="N86" t="s">
+        <v>28</v>
+      </c>
+      <c r="O86" t="b">
+        <v>1</v>
+      </c>
+      <c r="P86" t="s">
+        <v>120</v>
+      </c>
+      <c r="S86" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>738</v>
+      </c>
+      <c r="B87" t="s">
+        <v>739</v>
+      </c>
+      <c r="C87" t="s">
+        <v>243</v>
+      </c>
+      <c r="D87" t="s">
+        <v>740</v>
+      </c>
+      <c r="E87" t="s">
+        <v>741</v>
+      </c>
+      <c r="K87" t="s">
+        <v>25</v>
+      </c>
+      <c r="L87" t="s">
+        <v>26</v>
+      </c>
+      <c r="M87" t="s">
+        <v>27</v>
+      </c>
+      <c r="N87" t="s">
+        <v>28</v>
+      </c>
+      <c r="O87" t="b">
+        <v>1</v>
+      </c>
+      <c r="P87" t="s">
+        <v>120</v>
+      </c>
+      <c r="S87" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>742</v>
+      </c>
+      <c r="B88" t="s">
+        <v>743</v>
+      </c>
+      <c r="C88" t="s">
+        <v>243</v>
+      </c>
+      <c r="D88" t="s">
+        <v>744</v>
+      </c>
+      <c r="E88" t="s">
+        <v>745</v>
+      </c>
+      <c r="K88" t="s">
+        <v>25</v>
+      </c>
+      <c r="L88" t="s">
+        <v>26</v>
+      </c>
+      <c r="M88" t="s">
+        <v>27</v>
+      </c>
+      <c r="N88" t="s">
+        <v>28</v>
+      </c>
+      <c r="O88" t="b">
+        <v>1</v>
+      </c>
+      <c r="P88" t="s">
+        <v>120</v>
+      </c>
+      <c r="S88" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>746</v>
+      </c>
+      <c r="B89" t="s">
+        <v>747</v>
+      </c>
+      <c r="C89" t="s">
+        <v>243</v>
+      </c>
+      <c r="D89" t="s">
+        <v>748</v>
+      </c>
+      <c r="E89" t="s">
+        <v>749</v>
+      </c>
+      <c r="K89" t="s">
+        <v>25</v>
+      </c>
+      <c r="L89" t="s">
+        <v>26</v>
+      </c>
+      <c r="M89" t="s">
+        <v>27</v>
+      </c>
+      <c r="N89" t="s">
+        <v>28</v>
+      </c>
+      <c r="O89" t="b">
+        <v>1</v>
+      </c>
+      <c r="P89" t="s">
+        <v>120</v>
+      </c>
+      <c r="S89" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>750</v>
+      </c>
+      <c r="B90" t="s">
+        <v>751</v>
+      </c>
+      <c r="C90" t="s">
+        <v>243</v>
+      </c>
+      <c r="D90" t="s">
+        <v>752</v>
+      </c>
+      <c r="E90" t="s">
+        <v>753</v>
+      </c>
+      <c r="K90" t="s">
+        <v>25</v>
+      </c>
+      <c r="L90" t="s">
+        <v>26</v>
+      </c>
+      <c r="M90" t="s">
+        <v>27</v>
+      </c>
+      <c r="N90" t="s">
+        <v>28</v>
+      </c>
+      <c r="O90" t="b">
+        <v>1</v>
+      </c>
+      <c r="P90" t="s">
+        <v>120</v>
+      </c>
+      <c r="S90" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>754</v>
+      </c>
+      <c r="B91" t="s">
+        <v>755</v>
+      </c>
+      <c r="C91" t="s">
+        <v>243</v>
+      </c>
+      <c r="D91" t="s">
+        <v>756</v>
+      </c>
+      <c r="E91" t="s">
+        <v>757</v>
+      </c>
+      <c r="K91" t="s">
+        <v>25</v>
+      </c>
+      <c r="L91" t="s">
+        <v>26</v>
+      </c>
+      <c r="M91" t="s">
+        <v>27</v>
+      </c>
+      <c r="N91" t="s">
+        <v>28</v>
+      </c>
+      <c r="O91" t="b">
+        <v>1</v>
+      </c>
+      <c r="P91" t="s">
+        <v>120</v>
+      </c>
+      <c r="S91" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>758</v>
+      </c>
+      <c r="B92" t="s">
+        <v>759</v>
+      </c>
+      <c r="C92" t="s">
+        <v>243</v>
+      </c>
+      <c r="D92" t="s">
+        <v>760</v>
+      </c>
+      <c r="E92" t="s">
+        <v>761</v>
+      </c>
+      <c r="K92" t="s">
+        <v>25</v>
+      </c>
+      <c r="L92" t="s">
+        <v>26</v>
+      </c>
+      <c r="M92" t="s">
+        <v>27</v>
+      </c>
+      <c r="N92" t="s">
+        <v>28</v>
+      </c>
+      <c r="O92" t="b">
+        <v>1</v>
+      </c>
+      <c r="P92" t="s">
+        <v>120</v>
+      </c>
+      <c r="S92" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>762</v>
+      </c>
+      <c r="B93" t="s">
+        <v>763</v>
+      </c>
+      <c r="C93" t="s">
+        <v>459</v>
+      </c>
+      <c r="D93" t="s">
+        <v>764</v>
+      </c>
+      <c r="E93" t="s">
+        <v>765</v>
+      </c>
+      <c r="K93" t="s">
+        <v>25</v>
+      </c>
+      <c r="L93" t="s">
+        <v>26</v>
+      </c>
+      <c r="M93" t="s">
+        <v>27</v>
+      </c>
+      <c r="N93" t="s">
+        <v>28</v>
+      </c>
+      <c r="O93" t="b">
+        <v>1</v>
+      </c>
+      <c r="P93" t="s">
+        <v>120</v>
+      </c>
+      <c r="S93" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>766</v>
+      </c>
+      <c r="B94" t="s">
+        <v>767</v>
+      </c>
+      <c r="C94" t="s">
+        <v>459</v>
+      </c>
+      <c r="D94" t="s">
+        <v>768</v>
+      </c>
+      <c r="E94" t="s">
+        <v>769</v>
+      </c>
+      <c r="K94" t="s">
+        <v>25</v>
+      </c>
+      <c r="L94" t="s">
+        <v>26</v>
+      </c>
+      <c r="M94" t="s">
+        <v>27</v>
+      </c>
+      <c r="N94" t="s">
+        <v>28</v>
+      </c>
+      <c r="O94" t="b">
+        <v>1</v>
+      </c>
+      <c r="P94" t="s">
+        <v>120</v>
+      </c>
+      <c r="S94" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>770</v>
+      </c>
+      <c r="B95" t="s">
+        <v>771</v>
+      </c>
+      <c r="C95" t="s">
+        <v>459</v>
+      </c>
+      <c r="D95" t="s">
+        <v>772</v>
+      </c>
+      <c r="E95" t="s">
+        <v>773</v>
+      </c>
+      <c r="K95" t="s">
+        <v>25</v>
+      </c>
+      <c r="L95" t="s">
+        <v>26</v>
+      </c>
+      <c r="M95" t="s">
+        <v>27</v>
+      </c>
+      <c r="N95" t="s">
+        <v>28</v>
+      </c>
+      <c r="O95" t="b">
+        <v>1</v>
+      </c>
+      <c r="P95" t="s">
+        <v>120</v>
+      </c>
+      <c r="S95" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>774</v>
+      </c>
+      <c r="B96" t="s">
+        <v>775</v>
+      </c>
+      <c r="C96" t="s">
+        <v>459</v>
+      </c>
+      <c r="D96" t="s">
+        <v>776</v>
+      </c>
+      <c r="E96" t="s">
+        <v>777</v>
+      </c>
+      <c r="K96" t="s">
+        <v>25</v>
+      </c>
+      <c r="L96" t="s">
+        <v>26</v>
+      </c>
+      <c r="M96" t="s">
+        <v>27</v>
+      </c>
+      <c r="N96" t="s">
+        <v>28</v>
+      </c>
+      <c r="O96" t="b">
+        <v>1</v>
+      </c>
+      <c r="P96" t="s">
+        <v>120</v>
+      </c>
+      <c r="S96" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>778</v>
+      </c>
+      <c r="B97" t="s">
+        <v>779</v>
+      </c>
+      <c r="C97" t="s">
+        <v>459</v>
+      </c>
+      <c r="D97" t="s">
+        <v>780</v>
+      </c>
+      <c r="E97" t="s">
+        <v>781</v>
+      </c>
+      <c r="K97" t="s">
+        <v>25</v>
+      </c>
+      <c r="L97" t="s">
+        <v>26</v>
+      </c>
+      <c r="M97" t="s">
+        <v>27</v>
+      </c>
+      <c r="N97" t="s">
+        <v>28</v>
+      </c>
+      <c r="O97" t="b">
+        <v>1</v>
+      </c>
+      <c r="P97" t="s">
+        <v>120</v>
+      </c>
+      <c r="S97" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>782</v>
+      </c>
+      <c r="B98" t="s">
+        <v>783</v>
+      </c>
+      <c r="C98" t="s">
+        <v>459</v>
+      </c>
+      <c r="D98" t="s">
+        <v>784</v>
+      </c>
+      <c r="E98" t="s">
+        <v>785</v>
+      </c>
+      <c r="K98" t="s">
+        <v>25</v>
+      </c>
+      <c r="L98" t="s">
+        <v>26</v>
+      </c>
+      <c r="M98" t="s">
+        <v>27</v>
+      </c>
+      <c r="N98" t="s">
+        <v>28</v>
+      </c>
+      <c r="O98" t="b">
+        <v>1</v>
+      </c>
+      <c r="P98" t="s">
+        <v>120</v>
+      </c>
+      <c r="S98" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>786</v>
+      </c>
+      <c r="B99" t="s">
+        <v>787</v>
+      </c>
+      <c r="C99" t="s">
+        <v>459</v>
+      </c>
+      <c r="D99" t="s">
+        <v>788</v>
+      </c>
+      <c r="E99" t="s">
+        <v>789</v>
+      </c>
+      <c r="K99" t="s">
+        <v>25</v>
+      </c>
+      <c r="L99" t="s">
+        <v>26</v>
+      </c>
+      <c r="M99" t="s">
+        <v>27</v>
+      </c>
+      <c r="N99" t="s">
+        <v>28</v>
+      </c>
+      <c r="O99" t="b">
+        <v>1</v>
+      </c>
+      <c r="P99" t="s">
+        <v>120</v>
+      </c>
+      <c r="S99" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>790</v>
+      </c>
+      <c r="B100" t="s">
+        <v>791</v>
+      </c>
+      <c r="C100" t="s">
+        <v>459</v>
+      </c>
+      <c r="D100" t="s">
+        <v>792</v>
+      </c>
+      <c r="E100" t="s">
+        <v>793</v>
+      </c>
+      <c r="K100" t="s">
+        <v>25</v>
+      </c>
+      <c r="L100" t="s">
+        <v>26</v>
+      </c>
+      <c r="M100" t="s">
+        <v>27</v>
+      </c>
+      <c r="N100" t="s">
+        <v>28</v>
+      </c>
+      <c r="O100" t="b">
+        <v>1</v>
+      </c>
+      <c r="P100" t="s">
+        <v>120</v>
+      </c>
+      <c r="S100" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>794</v>
+      </c>
+      <c r="B101" t="s">
+        <v>795</v>
+      </c>
+      <c r="C101" t="s">
+        <v>459</v>
+      </c>
+      <c r="D101" t="s">
+        <v>796</v>
+      </c>
+      <c r="E101" t="s">
+        <v>797</v>
+      </c>
+      <c r="K101" t="s">
+        <v>25</v>
+      </c>
+      <c r="L101" t="s">
+        <v>26</v>
+      </c>
+      <c r="M101" t="s">
+        <v>27</v>
+      </c>
+      <c r="N101" t="s">
+        <v>28</v>
+      </c>
+      <c r="O101" t="b">
+        <v>1</v>
+      </c>
+      <c r="P101" t="s">
+        <v>120</v>
+      </c>
+      <c r="S101" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>798</v>
+      </c>
+      <c r="B102" t="s">
+        <v>799</v>
+      </c>
+      <c r="C102" t="s">
+        <v>459</v>
+      </c>
+      <c r="D102" t="s">
+        <v>800</v>
+      </c>
+      <c r="E102" t="s">
+        <v>801</v>
+      </c>
+      <c r="K102" t="s">
+        <v>25</v>
+      </c>
+      <c r="L102" t="s">
+        <v>26</v>
+      </c>
+      <c r="M102" t="s">
+        <v>27</v>
+      </c>
+      <c r="N102" t="s">
+        <v>28</v>
+      </c>
+      <c r="O102" t="b">
+        <v>1</v>
+      </c>
+      <c r="P102" t="s">
+        <v>120</v>
+      </c>
+      <c r="S102" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>802</v>
+      </c>
+      <c r="B103" t="s">
+        <v>803</v>
+      </c>
+      <c r="C103" t="s">
+        <v>459</v>
+      </c>
+      <c r="D103" t="s">
+        <v>804</v>
+      </c>
+      <c r="E103" t="s">
+        <v>805</v>
+      </c>
+      <c r="K103" t="s">
+        <v>25</v>
+      </c>
+      <c r="L103" t="s">
+        <v>26</v>
+      </c>
+      <c r="M103" t="s">
+        <v>27</v>
+      </c>
+      <c r="N103" t="s">
+        <v>28</v>
+      </c>
+      <c r="O103" t="b">
+        <v>1</v>
+      </c>
+      <c r="P103" t="s">
+        <v>120</v>
+      </c>
+      <c r="S103" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>806</v>
+      </c>
+      <c r="B104" t="s">
+        <v>807</v>
+      </c>
+      <c r="C104" t="s">
+        <v>459</v>
+      </c>
+      <c r="D104" t="s">
+        <v>808</v>
+      </c>
+      <c r="E104" t="s">
+        <v>809</v>
+      </c>
+      <c r="K104" t="s">
+        <v>25</v>
+      </c>
+      <c r="L104" t="s">
+        <v>26</v>
+      </c>
+      <c r="M104" t="s">
+        <v>27</v>
+      </c>
+      <c r="N104" t="s">
+        <v>28</v>
+      </c>
+      <c r="O104" t="b">
+        <v>1</v>
+      </c>
+      <c r="P104" t="s">
+        <v>120</v>
+      </c>
+      <c r="S104" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>810</v>
+      </c>
+      <c r="B105" t="s">
+        <v>811</v>
+      </c>
+      <c r="C105" t="s">
+        <v>459</v>
+      </c>
+      <c r="D105" t="s">
+        <v>812</v>
+      </c>
+      <c r="E105" t="s">
+        <v>813</v>
+      </c>
+      <c r="K105" t="s">
+        <v>25</v>
+      </c>
+      <c r="L105" t="s">
+        <v>26</v>
+      </c>
+      <c r="M105" t="s">
+        <v>27</v>
+      </c>
+      <c r="N105" t="s">
+        <v>28</v>
+      </c>
+      <c r="O105" t="b">
+        <v>1</v>
+      </c>
+      <c r="P105" t="s">
+        <v>120</v>
+      </c>
+      <c r="S105" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>814</v>
+      </c>
+      <c r="B106" t="s">
+        <v>815</v>
+      </c>
+      <c r="C106" t="s">
+        <v>459</v>
+      </c>
+      <c r="D106" t="s">
+        <v>816</v>
+      </c>
+      <c r="E106" t="s">
+        <v>817</v>
+      </c>
+      <c r="K106" t="s">
+        <v>25</v>
+      </c>
+      <c r="L106" t="s">
+        <v>26</v>
+      </c>
+      <c r="M106" t="s">
+        <v>27</v>
+      </c>
+      <c r="N106" t="s">
+        <v>28</v>
+      </c>
+      <c r="O106" t="b">
+        <v>1</v>
+      </c>
+      <c r="P106" t="s">
+        <v>120</v>
+      </c>
+      <c r="S106" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>818</v>
+      </c>
+      <c r="B107" t="s">
+        <v>819</v>
+      </c>
+      <c r="C107" t="s">
+        <v>459</v>
+      </c>
+      <c r="D107" t="s">
+        <v>820</v>
+      </c>
+      <c r="E107" t="s">
+        <v>821</v>
+      </c>
+      <c r="K107" t="s">
+        <v>25</v>
+      </c>
+      <c r="L107" t="s">
+        <v>26</v>
+      </c>
+      <c r="M107" t="s">
+        <v>27</v>
+      </c>
+      <c r="N107" t="s">
+        <v>28</v>
+      </c>
+      <c r="O107" t="b">
+        <v>1</v>
+      </c>
+      <c r="P107" t="s">
+        <v>120</v>
+      </c>
+      <c r="S107" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>822</v>
+      </c>
+      <c r="B108" t="s">
+        <v>823</v>
+      </c>
+      <c r="C108" t="s">
+        <v>459</v>
+      </c>
+      <c r="D108" t="s">
+        <v>824</v>
+      </c>
+      <c r="E108" t="s">
+        <v>825</v>
+      </c>
+      <c r="K108" t="s">
+        <v>25</v>
+      </c>
+      <c r="L108" t="s">
+        <v>26</v>
+      </c>
+      <c r="M108" t="s">
+        <v>27</v>
+      </c>
+      <c r="N108" t="s">
+        <v>28</v>
+      </c>
+      <c r="O108" t="b">
+        <v>1</v>
+      </c>
+      <c r="P108" t="s">
+        <v>120</v>
+      </c>
+      <c r="S108" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>826</v>
+      </c>
+      <c r="B109" t="s">
+        <v>827</v>
+      </c>
+      <c r="C109" t="s">
+        <v>459</v>
+      </c>
+      <c r="D109" t="s">
+        <v>828</v>
+      </c>
+      <c r="E109" t="s">
+        <v>829</v>
+      </c>
+      <c r="K109" t="s">
+        <v>25</v>
+      </c>
+      <c r="L109" t="s">
+        <v>26</v>
+      </c>
+      <c r="M109" t="s">
+        <v>27</v>
+      </c>
+      <c r="N109" t="s">
+        <v>28</v>
+      </c>
+      <c r="O109" t="b">
+        <v>1</v>
+      </c>
+      <c r="P109" t="s">
+        <v>120</v>
+      </c>
+      <c r="S109" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>830</v>
+      </c>
+      <c r="B110" t="s">
+        <v>831</v>
+      </c>
+      <c r="C110" t="s">
+        <v>459</v>
+      </c>
+      <c r="D110" t="s">
+        <v>832</v>
+      </c>
+      <c r="E110" t="s">
+        <v>833</v>
+      </c>
+      <c r="K110" t="s">
+        <v>25</v>
+      </c>
+      <c r="L110" t="s">
+        <v>26</v>
+      </c>
+      <c r="M110" t="s">
+        <v>27</v>
+      </c>
+      <c r="N110" t="s">
+        <v>28</v>
+      </c>
+      <c r="O110" t="b">
+        <v>1</v>
+      </c>
+      <c r="P110" t="s">
+        <v>120</v>
+      </c>
+      <c r="S110" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>834</v>
+      </c>
+      <c r="B111" t="s">
+        <v>835</v>
+      </c>
+      <c r="C111" t="s">
+        <v>470</v>
+      </c>
+      <c r="D111" t="s">
+        <v>836</v>
+      </c>
+      <c r="E111" t="s">
+        <v>837</v>
+      </c>
+      <c r="K111" t="s">
+        <v>25</v>
+      </c>
+      <c r="L111" t="s">
+        <v>26</v>
+      </c>
+      <c r="M111" t="s">
+        <v>27</v>
+      </c>
+      <c r="N111" t="s">
+        <v>28</v>
+      </c>
+      <c r="O111" t="b">
+        <v>1</v>
+      </c>
+      <c r="P111" t="s">
+        <v>120</v>
+      </c>
+      <c r="S111" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>838</v>
+      </c>
+      <c r="B112" t="s">
+        <v>839</v>
+      </c>
+      <c r="C112" t="s">
+        <v>470</v>
+      </c>
+      <c r="D112" t="s">
+        <v>840</v>
+      </c>
+      <c r="E112" t="s">
+        <v>841</v>
+      </c>
+      <c r="K112" t="s">
+        <v>25</v>
+      </c>
+      <c r="L112" t="s">
+        <v>26</v>
+      </c>
+      <c r="M112" t="s">
+        <v>27</v>
+      </c>
+      <c r="N112" t="s">
+        <v>28</v>
+      </c>
+      <c r="O112" t="b">
+        <v>1</v>
+      </c>
+      <c r="P112" t="s">
+        <v>120</v>
+      </c>
+      <c r="S112" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>842</v>
+      </c>
+      <c r="B113" t="s">
+        <v>843</v>
+      </c>
+      <c r="C113" t="s">
+        <v>470</v>
+      </c>
+      <c r="D113" t="s">
+        <v>844</v>
+      </c>
+      <c r="E113" t="s">
+        <v>845</v>
+      </c>
+      <c r="K113" t="s">
+        <v>25</v>
+      </c>
+      <c r="L113" t="s">
+        <v>26</v>
+      </c>
+      <c r="M113" t="s">
+        <v>27</v>
+      </c>
+      <c r="N113" t="s">
+        <v>28</v>
+      </c>
+      <c r="O113" t="b">
+        <v>1</v>
+      </c>
+      <c r="P113" t="s">
+        <v>120</v>
+      </c>
+      <c r="S113" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>846</v>
+      </c>
+      <c r="B114" t="s">
+        <v>847</v>
+      </c>
+      <c r="C114" t="s">
+        <v>470</v>
+      </c>
+      <c r="D114" t="s">
+        <v>848</v>
+      </c>
+      <c r="E114" t="s">
+        <v>849</v>
+      </c>
+      <c r="K114" t="s">
+        <v>25</v>
+      </c>
+      <c r="L114" t="s">
+        <v>26</v>
+      </c>
+      <c r="M114" t="s">
+        <v>27</v>
+      </c>
+      <c r="N114" t="s">
+        <v>28</v>
+      </c>
+      <c r="O114" t="b">
+        <v>1</v>
+      </c>
+      <c r="P114" t="s">
+        <v>120</v>
+      </c>
+      <c r="S114" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>850</v>
+      </c>
+      <c r="B115" t="s">
+        <v>851</v>
+      </c>
+      <c r="C115" t="s">
+        <v>459</v>
+      </c>
+      <c r="D115" t="s">
+        <v>852</v>
+      </c>
+      <c r="E115" t="s">
+        <v>853</v>
+      </c>
+      <c r="K115" t="s">
+        <v>25</v>
+      </c>
+      <c r="L115" t="s">
+        <v>26</v>
+      </c>
+      <c r="M115" t="s">
+        <v>27</v>
+      </c>
+      <c r="N115" t="s">
+        <v>28</v>
+      </c>
+      <c r="O115" t="b">
+        <v>1</v>
+      </c>
+      <c r="P115" t="s">
+        <v>120</v>
+      </c>
+      <c r="S115" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>854</v>
+      </c>
+      <c r="B116" t="s">
+        <v>855</v>
+      </c>
+      <c r="C116" t="s">
+        <v>459</v>
+      </c>
+      <c r="D116" t="s">
+        <v>856</v>
+      </c>
+      <c r="E116" t="s">
+        <v>857</v>
+      </c>
+      <c r="K116" t="s">
+        <v>25</v>
+      </c>
+      <c r="L116" t="s">
+        <v>26</v>
+      </c>
+      <c r="M116" t="s">
+        <v>27</v>
+      </c>
+      <c r="N116" t="s">
+        <v>28</v>
+      </c>
+      <c r="O116" t="b">
+        <v>1</v>
+      </c>
+      <c r="P116" t="s">
+        <v>120</v>
+      </c>
+      <c r="S116" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>858</v>
+      </c>
+      <c r="B117" t="s">
+        <v>859</v>
+      </c>
+      <c r="C117" t="s">
+        <v>459</v>
+      </c>
+      <c r="D117" t="s">
+        <v>860</v>
+      </c>
+      <c r="E117" t="s">
+        <v>861</v>
+      </c>
+      <c r="K117" t="s">
+        <v>25</v>
+      </c>
+      <c r="L117" t="s">
+        <v>26</v>
+      </c>
+      <c r="M117" t="s">
+        <v>27</v>
+      </c>
+      <c r="N117" t="s">
+        <v>28</v>
+      </c>
+      <c r="O117" t="b">
+        <v>1</v>
+      </c>
+      <c r="P117" t="s">
+        <v>120</v>
+      </c>
+      <c r="S117" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>862</v>
+      </c>
+      <c r="B118" t="s">
+        <v>863</v>
+      </c>
+      <c r="C118" t="s">
+        <v>459</v>
+      </c>
+      <c r="D118" t="s">
+        <v>864</v>
+      </c>
+      <c r="E118" t="s">
+        <v>865</v>
+      </c>
+      <c r="K118" t="s">
+        <v>25</v>
+      </c>
+      <c r="L118" t="s">
+        <v>26</v>
+      </c>
+      <c r="M118" t="s">
+        <v>27</v>
+      </c>
+      <c r="N118" t="s">
+        <v>28</v>
+      </c>
+      <c r="O118" t="b">
+        <v>1</v>
+      </c>
+      <c r="P118" t="s">
+        <v>120</v>
+      </c>
+      <c r="S118" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>866</v>
+      </c>
+      <c r="B119" t="s">
+        <v>867</v>
+      </c>
+      <c r="C119" t="s">
+        <v>243</v>
+      </c>
+      <c r="D119" t="s">
+        <v>868</v>
+      </c>
+      <c r="E119" t="s">
+        <v>866</v>
+      </c>
+      <c r="K119" t="s">
+        <v>25</v>
+      </c>
+      <c r="L119" t="s">
+        <v>26</v>
+      </c>
+      <c r="M119" t="s">
+        <v>27</v>
+      </c>
+      <c r="N119" t="s">
+        <v>28</v>
+      </c>
+      <c r="O119" t="b">
+        <v>1</v>
+      </c>
+      <c r="P119" t="s">
+        <v>120</v>
+      </c>
+      <c r="S119" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>869</v>
+      </c>
+      <c r="B120" t="s">
+        <v>870</v>
+      </c>
+      <c r="C120" t="s">
+        <v>243</v>
+      </c>
+      <c r="D120" t="s">
+        <v>871</v>
+      </c>
+      <c r="E120" t="s">
+        <v>869</v>
+      </c>
+      <c r="K120" t="s">
+        <v>25</v>
+      </c>
+      <c r="L120" t="s">
+        <v>26</v>
+      </c>
+      <c r="M120" t="s">
+        <v>27</v>
+      </c>
+      <c r="N120" t="s">
+        <v>28</v>
+      </c>
+      <c r="O120" t="b">
+        <v>1</v>
+      </c>
+      <c r="P120" t="s">
+        <v>120</v>
+      </c>
+      <c r="S120" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>872</v>
+      </c>
+      <c r="B121" t="s">
+        <v>873</v>
+      </c>
+      <c r="C121" t="s">
+        <v>243</v>
+      </c>
+      <c r="D121" t="s">
+        <v>874</v>
+      </c>
+      <c r="E121" t="s">
+        <v>872</v>
+      </c>
+      <c r="K121" t="s">
+        <v>25</v>
+      </c>
+      <c r="L121" t="s">
+        <v>26</v>
+      </c>
+      <c r="M121" t="s">
+        <v>27</v>
+      </c>
+      <c r="N121" t="s">
+        <v>28</v>
+      </c>
+      <c r="O121" t="b">
+        <v>1</v>
+      </c>
+      <c r="P121" t="s">
+        <v>120</v>
+      </c>
+      <c r="S121" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>875</v>
+      </c>
+      <c r="B122" t="s">
+        <v>876</v>
+      </c>
+      <c r="C122" t="s">
+        <v>243</v>
+      </c>
+      <c r="D122" t="s">
+        <v>877</v>
+      </c>
+      <c r="E122" t="s">
+        <v>875</v>
+      </c>
+      <c r="K122" t="s">
+        <v>25</v>
+      </c>
+      <c r="L122" t="s">
+        <v>26</v>
+      </c>
+      <c r="M122" t="s">
+        <v>27</v>
+      </c>
+      <c r="N122" t="s">
+        <v>28</v>
+      </c>
+      <c r="O122" t="b">
+        <v>1</v>
+      </c>
+      <c r="P122" t="s">
+        <v>120</v>
+      </c>
+      <c r="S122" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>878</v>
+      </c>
+      <c r="B123" t="s">
+        <v>879</v>
+      </c>
+      <c r="C123" t="s">
+        <v>243</v>
+      </c>
+      <c r="D123" t="s">
+        <v>880</v>
+      </c>
+      <c r="E123" t="s">
+        <v>881</v>
+      </c>
+      <c r="K123" t="s">
+        <v>25</v>
+      </c>
+      <c r="L123" t="s">
+        <v>26</v>
+      </c>
+      <c r="M123" t="s">
+        <v>27</v>
+      </c>
+      <c r="N123" t="s">
+        <v>28</v>
+      </c>
+      <c r="O123" t="b">
+        <v>1</v>
+      </c>
+      <c r="P123" t="s">
+        <v>120</v>
+      </c>
+      <c r="S123" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>882</v>
+      </c>
+      <c r="B124" t="s">
+        <v>883</v>
+      </c>
+      <c r="C124" t="s">
+        <v>243</v>
+      </c>
+      <c r="D124" t="s">
+        <v>884</v>
+      </c>
+      <c r="E124" t="s">
+        <v>885</v>
+      </c>
+      <c r="K124" t="s">
+        <v>25</v>
+      </c>
+      <c r="L124" t="s">
+        <v>26</v>
+      </c>
+      <c r="M124" t="s">
+        <v>27</v>
+      </c>
+      <c r="N124" t="s">
+        <v>28</v>
+      </c>
+      <c r="O124" t="b">
+        <v>1</v>
+      </c>
+      <c r="P124" t="s">
+        <v>120</v>
+      </c>
+      <c r="S124" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>886</v>
+      </c>
+      <c r="B125" t="s">
+        <v>887</v>
+      </c>
+      <c r="C125" t="s">
+        <v>243</v>
+      </c>
+      <c r="D125" t="s">
+        <v>888</v>
+      </c>
+      <c r="E125" t="s">
+        <v>886</v>
+      </c>
+      <c r="K125" t="s">
+        <v>25</v>
+      </c>
+      <c r="L125" t="s">
+        <v>26</v>
+      </c>
+      <c r="M125" t="s">
+        <v>27</v>
+      </c>
+      <c r="N125" t="s">
+        <v>28</v>
+      </c>
+      <c r="O125" t="b">
+        <v>1</v>
+      </c>
+      <c r="P125" t="s">
+        <v>120</v>
+      </c>
+      <c r="S125" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>889</v>
+      </c>
+      <c r="B126" t="s">
+        <v>890</v>
+      </c>
+      <c r="C126" t="s">
+        <v>243</v>
+      </c>
+      <c r="D126" t="s">
+        <v>891</v>
+      </c>
+      <c r="E126" t="s">
+        <v>889</v>
+      </c>
+      <c r="K126" t="s">
+        <v>25</v>
+      </c>
+      <c r="L126" t="s">
+        <v>26</v>
+      </c>
+      <c r="M126" t="s">
+        <v>27</v>
+      </c>
+      <c r="N126" t="s">
+        <v>28</v>
+      </c>
+      <c r="O126" t="b">
+        <v>1</v>
+      </c>
+      <c r="P126" t="s">
+        <v>120</v>
+      </c>
+      <c r="S126" t="s">
+        <v>423</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S1"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -5971,7 +12325,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:S1"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -6062,7 +12416,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:S1"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>

--- a/sandbox-refresh-csvs/users.xlsx
+++ b/sandbox-refresh-csvs/users.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chandrahas.r.bireddy\VS CODE\MOH-ALR\sandbox-refresh-csvs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repo\MOH-ALR\sandbox-refresh-csvs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9FFE16-05BE-4D3A-BD43-28B2D035950F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CBEAF47-BACB-4E9F-95C1-E2E630FE167C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="34620" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dev" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,9 @@
     <sheet name="UAT" sheetId="4" r:id="rId6"/>
     <sheet name="PreProd" sheetId="5" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dev!$A$1:$A$59</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2784" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3067" uniqueCount="917">
   <si>
     <t>FirstName</t>
   </si>
@@ -2715,6 +2718,81 @@
   </si>
   <si>
     <t>iha-eho-6@gov.bc.ca.uat</t>
+  </si>
+  <si>
+    <t>fha-test-user@reportinguser.uat.com</t>
+  </si>
+  <si>
+    <t>nha-test-user@reportinguser.uat.com</t>
+  </si>
+  <si>
+    <t>vch-test-user@reportinguser.uat.com</t>
+  </si>
+  <si>
+    <t>vcih-test-user@reportinguser.uat.com</t>
+  </si>
+  <si>
+    <t>agnes.kreps@accenture.com</t>
+  </si>
+  <si>
+    <t>ehis-officer-user@test.uat.com</t>
+  </si>
+  <si>
+    <t>ehis-admin-user@test.uat.com</t>
+  </si>
+  <si>
+    <t>EHIS_Officer_Users_PG;EHISUsersPG</t>
+  </si>
+  <si>
+    <t>gandloju.vishwantha@reportinguser.uat.com</t>
+  </si>
+  <si>
+    <t>iha-test-user@reportinguser.uat.com</t>
+  </si>
+  <si>
+    <t>Agnes</t>
+  </si>
+  <si>
+    <t>Krep</t>
+  </si>
+  <si>
+    <t>agnes.kreps@accenture.com.uat</t>
+  </si>
+  <si>
+    <t>agkep</t>
+  </si>
+  <si>
+    <t>megan.li@accenture.com.uat</t>
+  </si>
+  <si>
+    <t>anastasiia.beryl@accenture.com.phocs.uat</t>
+  </si>
+  <si>
+    <t>sneha.x.gurung@accenture.com.phocs.uat</t>
+  </si>
+  <si>
+    <t>vivian.man@accenture.com.uat</t>
+  </si>
+  <si>
+    <t>latifa.mnyusiwalla@accenture.com.uat</t>
+  </si>
+  <si>
+    <t>Ana@accenture.com.operator</t>
+  </si>
+  <si>
+    <t>EHISUsersPG;EHIS_Water_Admin_Users_PG;EHIS_Water_Admin_Users_PG</t>
+  </si>
+  <si>
+    <t>Prajwal</t>
+  </si>
+  <si>
+    <t>prajwal.s.murthy@accenture.com.uat</t>
+  </si>
+  <si>
+    <t>pmur</t>
+  </si>
+  <si>
+    <t>Murthy</t>
   </si>
 </sst>
 </file>
@@ -2765,10 +2843,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3109,29 +3189,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:S59"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.796875" customWidth="1"/>
-    <col min="2" max="2" width="16.796875" customWidth="1"/>
-    <col min="3" max="3" width="34.796875" customWidth="1"/>
-    <col min="4" max="4" width="40.796875" customWidth="1"/>
-    <col min="5" max="5" width="10.796875" customWidth="1"/>
-    <col min="6" max="6" width="24.796875" customWidth="1"/>
-    <col min="7" max="7" width="32.796875" customWidth="1"/>
-    <col min="8" max="8" width="24.796875" customWidth="1"/>
-    <col min="9" max="10" width="16.796875" customWidth="1"/>
-    <col min="11" max="11" width="22.796875" customWidth="1"/>
-    <col min="12" max="12" width="12.796875" customWidth="1"/>
-    <col min="13" max="13" width="18.796875" customWidth="1"/>
-    <col min="14" max="14" width="20.796875" customWidth="1"/>
-    <col min="15" max="15" width="10.796875" customWidth="1"/>
-    <col min="16" max="16" width="28.796875" customWidth="1"/>
-    <col min="17" max="18" width="50.796875" customWidth="1"/>
-    <col min="19" max="19" width="40.796875" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="32.83203125" customWidth="1"/>
+    <col min="8" max="8" width="24.83203125" customWidth="1"/>
+    <col min="9" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="18.83203125" customWidth="1"/>
+    <col min="14" max="14" width="20.83203125" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" customWidth="1"/>
+    <col min="16" max="16" width="28.83203125" customWidth="1"/>
+    <col min="17" max="18" width="50.83203125" customWidth="1"/>
+    <col min="19" max="19" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3190,7 +3271,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -3249,7 +3330,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -3308,7 +3389,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -3367,7 +3448,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -3426,7 +3507,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -3485,7 +3566,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -3544,7 +3625,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>68</v>
       </c>
@@ -3603,7 +3684,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>76</v>
       </c>
@@ -3662,7 +3743,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>83</v>
       </c>
@@ -3721,7 +3802,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>90</v>
       </c>
@@ -3780,7 +3861,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>97</v>
       </c>
@@ -3839,7 +3920,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>106</v>
       </c>
@@ -3898,7 +3979,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>111</v>
       </c>
@@ -3957,7 +4038,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>115</v>
       </c>
@@ -4016,7 +4097,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>123</v>
       </c>
@@ -4075,7 +4156,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>129</v>
       </c>
@@ -4134,7 +4215,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>135</v>
       </c>
@@ -4193,7 +4274,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>143</v>
       </c>
@@ -4252,7 +4333,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>148</v>
       </c>
@@ -4311,7 +4392,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>155</v>
       </c>
@@ -4370,7 +4451,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>159</v>
       </c>
@@ -4429,7 +4510,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>166</v>
       </c>
@@ -4488,7 +4569,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>172</v>
       </c>
@@ -4547,7 +4628,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>179</v>
       </c>
@@ -4606,7 +4687,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>179</v>
       </c>
@@ -4665,7 +4746,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>190</v>
       </c>
@@ -4724,7 +4805,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>195</v>
       </c>
@@ -4783,7 +4864,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>202</v>
       </c>
@@ -4842,7 +4923,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>24</v>
       </c>
@@ -4901,7 +4982,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>213</v>
       </c>
@@ -4960,7 +5041,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>220</v>
       </c>
@@ -5019,7 +5100,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>224</v>
       </c>
@@ -5078,7 +5159,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>228</v>
       </c>
@@ -5137,7 +5218,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>231</v>
       </c>
@@ -5196,7 +5277,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>236</v>
       </c>
@@ -5255,7 +5336,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>241</v>
       </c>
@@ -5314,7 +5395,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>124</v>
       </c>
@@ -5373,7 +5454,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>252</v>
       </c>
@@ -5432,7 +5513,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>257</v>
       </c>
@@ -5491,7 +5572,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>265</v>
       </c>
@@ -5550,7 +5631,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>270</v>
       </c>
@@ -5609,7 +5690,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>277</v>
       </c>
@@ -5668,7 +5749,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>281</v>
       </c>
@@ -5727,7 +5808,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>286</v>
       </c>
@@ -5786,7 +5867,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>290</v>
       </c>
@@ -5845,7 +5926,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>295</v>
       </c>
@@ -5904,7 +5985,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>300</v>
       </c>
@@ -5963,7 +6044,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>306</v>
       </c>
@@ -6022,7 +6103,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>311</v>
       </c>
@@ -6081,7 +6162,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>315</v>
       </c>
@@ -6140,7 +6221,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>318</v>
       </c>
@@ -6199,7 +6280,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>321</v>
       </c>
@@ -6258,7 +6339,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>323</v>
       </c>
@@ -6317,7 +6398,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>24</v>
       </c>
@@ -6376,7 +6457,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>332</v>
       </c>
@@ -6435,7 +6516,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>24</v>
       </c>
@@ -6494,7 +6575,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>343</v>
       </c>
@@ -6553,7 +6634,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>350</v>
       </c>
@@ -6613,6 +6694,20 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:A59" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Ana"/>
+        <filter val="Anastasia"/>
+        <filter val="Latifa"/>
+        <filter val="Megan Li"/>
+        <filter val="Operator"/>
+        <filter val="OPHO_reporting"/>
+        <filter val="Sneha"/>
+        <filter val="Vivian"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="A1:S1" numberStoredAsText="1"/>
@@ -6623,13 +6718,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{473E8023-FCC9-42B7-9B69-27BECC764237}">
   <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="27.19921875" customWidth="1"/>
-    <col min="4" max="4" width="32.09765625" customWidth="1"/>
+    <col min="3" max="3" width="27.1640625" customWidth="1"/>
+    <col min="4" max="4" width="32.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6688,7 +6783,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>360</v>
       </c>
@@ -6744,30 +6839,30 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S17"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.09765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.8984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.9140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.58203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.08203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.09765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.8984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.08203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.9140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.1640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.8984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.9140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -6826,7 +6921,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>363</v>
       </c>
@@ -6861,7 +6956,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>241</v>
       </c>
@@ -6896,7 +6991,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>190</v>
       </c>
@@ -6931,7 +7026,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>365</v>
       </c>
@@ -6966,7 +7061,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>220</v>
       </c>
@@ -7001,7 +7096,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>68</v>
       </c>
@@ -7036,7 +7131,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>368</v>
       </c>
@@ -7071,7 +7166,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>228</v>
       </c>
@@ -7106,7 +7201,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>179</v>
       </c>
@@ -7141,7 +7236,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>166</v>
       </c>
@@ -7176,7 +7271,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>375</v>
       </c>
@@ -7211,7 +7306,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>265</v>
       </c>
@@ -7246,7 +7341,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>378</v>
       </c>
@@ -7281,7 +7376,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>252</v>
       </c>
@@ -7316,7 +7411,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>224</v>
       </c>
@@ -7351,7 +7446,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>213</v>
       </c>
@@ -7397,30 +7492,30 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC3A407E-9EAB-4433-9358-BEF5FC974994}">
   <dimension ref="A1:S126"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.8984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.9140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.58203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.08203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.09765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.8984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.08203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.9140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.08203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.8984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.9140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="26.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7479,7 +7574,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>392</v>
       </c>
@@ -7517,7 +7612,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>397</v>
       </c>
@@ -7555,7 +7650,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>401</v>
       </c>
@@ -7593,7 +7688,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>406</v>
       </c>
@@ -7631,7 +7726,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>410</v>
       </c>
@@ -7669,7 +7764,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>415</v>
       </c>
@@ -7707,7 +7802,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>419</v>
       </c>
@@ -7745,7 +7840,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>424</v>
       </c>
@@ -7783,7 +7878,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>428</v>
       </c>
@@ -7821,7 +7916,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>434</v>
       </c>
@@ -7859,7 +7954,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>438</v>
       </c>
@@ -7897,7 +7992,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>443</v>
       </c>
@@ -7935,7 +8030,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>447</v>
       </c>
@@ -7973,7 +8068,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>452</v>
       </c>
@@ -8011,7 +8106,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>457</v>
       </c>
@@ -8049,7 +8144,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>463</v>
       </c>
@@ -8087,7 +8182,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>468</v>
       </c>
@@ -8125,7 +8220,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>473</v>
       </c>
@@ -8163,7 +8258,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>478</v>
       </c>
@@ -8201,7 +8296,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>482</v>
       </c>
@@ -8239,7 +8334,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>486</v>
       </c>
@@ -8277,7 +8372,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>489</v>
       </c>
@@ -8315,7 +8410,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>493</v>
       </c>
@@ -8353,7 +8448,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>497</v>
       </c>
@@ -8391,7 +8486,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>501</v>
       </c>
@@ -8429,7 +8524,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>505</v>
       </c>
@@ -8467,7 +8562,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>509</v>
       </c>
@@ -8505,7 +8600,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>513</v>
       </c>
@@ -8543,7 +8638,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>516</v>
       </c>
@@ -8581,7 +8676,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>520</v>
       </c>
@@ -8619,7 +8714,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>524</v>
       </c>
@@ -8657,7 +8752,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>528</v>
       </c>
@@ -8695,7 +8790,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>532</v>
       </c>
@@ -8733,7 +8828,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>535</v>
       </c>
@@ -8771,7 +8866,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>539</v>
       </c>
@@ -8809,7 +8904,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>543</v>
       </c>
@@ -8847,7 +8942,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>547</v>
       </c>
@@ -8885,7 +8980,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>551</v>
       </c>
@@ -8923,7 +9018,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>554</v>
       </c>
@@ -8961,7 +9056,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>558</v>
       </c>
@@ -8999,7 +9094,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>562</v>
       </c>
@@ -9037,7 +9132,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>566</v>
       </c>
@@ -9075,7 +9170,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>570</v>
       </c>
@@ -9113,7 +9208,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>574</v>
       </c>
@@ -9151,7 +9246,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>578</v>
       </c>
@@ -9189,7 +9284,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>582</v>
       </c>
@@ -9227,7 +9322,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>586</v>
       </c>
@@ -9265,7 +9360,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>590</v>
       </c>
@@ -9303,7 +9398,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>594</v>
       </c>
@@ -9341,7 +9436,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>598</v>
       </c>
@@ -9379,7 +9474,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>602</v>
       </c>
@@ -9417,7 +9512,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>606</v>
       </c>
@@ -9455,7 +9550,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>610</v>
       </c>
@@ -9493,7 +9588,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>614</v>
       </c>
@@ -9531,7 +9626,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>618</v>
       </c>
@@ -9569,7 +9664,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="57" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>622</v>
       </c>
@@ -9607,7 +9702,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>625</v>
       </c>
@@ -9645,7 +9740,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>629</v>
       </c>
@@ -9683,7 +9778,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>632</v>
       </c>
@@ -9721,7 +9816,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>636</v>
       </c>
@@ -9759,7 +9854,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>640</v>
       </c>
@@ -9797,7 +9892,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>644</v>
       </c>
@@ -9835,7 +9930,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>647</v>
       </c>
@@ -9873,7 +9968,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>651</v>
       </c>
@@ -9911,7 +10006,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>655</v>
       </c>
@@ -9949,7 +10044,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>658</v>
       </c>
@@ -9987,7 +10082,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>662</v>
       </c>
@@ -10025,7 +10120,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>666</v>
       </c>
@@ -10063,7 +10158,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>670</v>
       </c>
@@ -10101,7 +10196,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>674</v>
       </c>
@@ -10139,7 +10234,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>678</v>
       </c>
@@ -10177,7 +10272,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>682</v>
       </c>
@@ -10215,7 +10310,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>686</v>
       </c>
@@ -10253,7 +10348,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>690</v>
       </c>
@@ -10291,7 +10386,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>694</v>
       </c>
@@ -10329,7 +10424,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>698</v>
       </c>
@@ -10367,7 +10462,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>702</v>
       </c>
@@ -10405,7 +10500,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>706</v>
       </c>
@@ -10443,7 +10538,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>710</v>
       </c>
@@ -10481,7 +10576,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="81" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>714</v>
       </c>
@@ -10519,7 +10614,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="82" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>718</v>
       </c>
@@ -10557,7 +10652,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="83" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>722</v>
       </c>
@@ -10595,7 +10690,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="84" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>726</v>
       </c>
@@ -10633,7 +10728,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="85" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>730</v>
       </c>
@@ -10671,7 +10766,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="86" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>734</v>
       </c>
@@ -10709,7 +10804,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="87" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>738</v>
       </c>
@@ -10747,7 +10842,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="88" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>742</v>
       </c>
@@ -10785,7 +10880,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="89" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>746</v>
       </c>
@@ -10823,7 +10918,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="90" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>750</v>
       </c>
@@ -10861,7 +10956,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="91" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>754</v>
       </c>
@@ -10899,7 +10994,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="92" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>758</v>
       </c>
@@ -10937,7 +11032,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="93" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>762</v>
       </c>
@@ -10975,7 +11070,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="94" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>766</v>
       </c>
@@ -11013,7 +11108,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="95" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>770</v>
       </c>
@@ -11051,7 +11146,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="96" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>774</v>
       </c>
@@ -11089,7 +11184,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="97" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>778</v>
       </c>
@@ -11127,7 +11222,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="98" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>782</v>
       </c>
@@ -11165,7 +11260,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="99" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>786</v>
       </c>
@@ -11203,7 +11298,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="100" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>790</v>
       </c>
@@ -11241,7 +11336,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="101" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>794</v>
       </c>
@@ -11279,7 +11374,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="102" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>798</v>
       </c>
@@ -11317,7 +11412,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="103" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>802</v>
       </c>
@@ -11355,7 +11450,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="104" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>806</v>
       </c>
@@ -11393,7 +11488,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="105" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>810</v>
       </c>
@@ -11431,7 +11526,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="106" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>814</v>
       </c>
@@ -11469,7 +11564,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="107" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>818</v>
       </c>
@@ -11507,7 +11602,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="108" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>822</v>
       </c>
@@ -11545,7 +11640,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="109" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>826</v>
       </c>
@@ -11583,7 +11678,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="110" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>830</v>
       </c>
@@ -11621,7 +11716,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="111" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>834</v>
       </c>
@@ -11659,7 +11754,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="112" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>838</v>
       </c>
@@ -11697,7 +11792,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="113" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>842</v>
       </c>
@@ -11735,7 +11830,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="114" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>846</v>
       </c>
@@ -11773,7 +11868,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="115" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>850</v>
       </c>
@@ -11811,7 +11906,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="116" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>854</v>
       </c>
@@ -11849,7 +11944,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="117" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>858</v>
       </c>
@@ -11887,7 +11982,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="118" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>862</v>
       </c>
@@ -11925,7 +12020,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="119" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>866</v>
       </c>
@@ -11963,7 +12058,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="120" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>869</v>
       </c>
@@ -12001,7 +12096,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="121" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>872</v>
       </c>
@@ -12039,7 +12134,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="122" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>875</v>
       </c>
@@ -12077,7 +12172,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="123" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>878</v>
       </c>
@@ -12115,7 +12210,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="124" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>882</v>
       </c>
@@ -12153,7 +12248,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="125" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>886</v>
       </c>
@@ -12191,7 +12286,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="126" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>889</v>
       </c>
@@ -12237,28 +12332,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S1"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.796875" customWidth="1"/>
-    <col min="2" max="2" width="16.796875" customWidth="1"/>
-    <col min="3" max="3" width="34.796875" customWidth="1"/>
-    <col min="4" max="4" width="40.796875" customWidth="1"/>
-    <col min="5" max="5" width="10.796875" customWidth="1"/>
-    <col min="6" max="6" width="24.796875" customWidth="1"/>
-    <col min="7" max="7" width="32.796875" customWidth="1"/>
-    <col min="8" max="8" width="24.796875" customWidth="1"/>
-    <col min="9" max="10" width="16.796875" customWidth="1"/>
-    <col min="11" max="11" width="22.796875" customWidth="1"/>
-    <col min="12" max="12" width="12.796875" customWidth="1"/>
-    <col min="13" max="13" width="18.796875" customWidth="1"/>
-    <col min="14" max="14" width="20.796875" customWidth="1"/>
-    <col min="15" max="15" width="10.796875" customWidth="1"/>
-    <col min="16" max="16" width="28.796875" customWidth="1"/>
-    <col min="17" max="18" width="50.796875" customWidth="1"/>
-    <col min="19" max="19" width="40.796875" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="32.83203125" customWidth="1"/>
+    <col min="8" max="8" width="24.83203125" customWidth="1"/>
+    <col min="9" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="18.83203125" customWidth="1"/>
+    <col min="14" max="14" width="20.83203125" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" customWidth="1"/>
+    <col min="16" max="16" width="28.83203125" customWidth="1"/>
+    <col min="17" max="18" width="50.83203125" customWidth="1"/>
+    <col min="19" max="19" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12327,29 +12422,29 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:S1"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S17"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.796875" customWidth="1"/>
-    <col min="2" max="2" width="16.796875" customWidth="1"/>
-    <col min="3" max="3" width="34.796875" customWidth="1"/>
-    <col min="4" max="4" width="40.796875" customWidth="1"/>
-    <col min="5" max="5" width="10.796875" customWidth="1"/>
-    <col min="6" max="6" width="24.796875" customWidth="1"/>
-    <col min="7" max="7" width="32.796875" customWidth="1"/>
-    <col min="8" max="8" width="24.796875" customWidth="1"/>
-    <col min="9" max="10" width="16.796875" customWidth="1"/>
-    <col min="11" max="11" width="22.796875" customWidth="1"/>
-    <col min="12" max="12" width="12.796875" customWidth="1"/>
-    <col min="13" max="13" width="18.796875" customWidth="1"/>
-    <col min="14" max="14" width="20.796875" customWidth="1"/>
-    <col min="15" max="15" width="10.796875" customWidth="1"/>
-    <col min="16" max="16" width="28.796875" customWidth="1"/>
-    <col min="17" max="18" width="50.796875" customWidth="1"/>
-    <col min="19" max="19" width="40.796875" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="32.83203125" customWidth="1"/>
+    <col min="8" max="8" width="24.83203125" customWidth="1"/>
+    <col min="9" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="18.83203125" customWidth="1"/>
+    <col min="14" max="14" width="20.83203125" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" customWidth="1"/>
+    <col min="16" max="16" width="28.83203125" customWidth="1"/>
+    <col min="17" max="18" width="50.83203125" customWidth="1"/>
+    <col min="19" max="19" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12408,7 +12503,903 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="E2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" t="s">
+        <v>218</v>
+      </c>
+      <c r="S2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="E3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" t="s">
+        <v>120</v>
+      </c>
+      <c r="R3" t="s">
+        <v>218</v>
+      </c>
+      <c r="S3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="E4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" t="s">
+        <v>120</v>
+      </c>
+      <c r="R4" t="s">
+        <v>218</v>
+      </c>
+      <c r="S4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="E5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" t="s">
+        <v>120</v>
+      </c>
+      <c r="R5" t="s">
+        <v>218</v>
+      </c>
+      <c r="S5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="E6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O6" t="s">
+        <v>29</v>
+      </c>
+      <c r="P6" t="s">
+        <v>120</v>
+      </c>
+      <c r="R6" t="s">
+        <v>218</v>
+      </c>
+      <c r="S6" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>265</v>
+      </c>
+      <c r="B7" t="s">
+        <v>258</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="E7" t="s">
+        <v>251</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" t="s">
+        <v>28</v>
+      </c>
+      <c r="O7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P7" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R7" t="s">
+        <v>268</v>
+      </c>
+      <c r="S7" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B8" t="s">
+        <v>301</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="E8" t="s">
+        <v>317</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P8" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>24</v>
+      </c>
+      <c r="R8" t="s">
+        <v>127</v>
+      </c>
+      <c r="S8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>311</v>
+      </c>
+      <c r="B9" t="s">
+        <v>301</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="E9" t="s">
+        <v>313</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P9" t="s">
+        <v>120</v>
+      </c>
+      <c r="R9" t="s">
+        <v>218</v>
+      </c>
+      <c r="S9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>902</v>
+      </c>
+      <c r="B10" t="s">
+        <v>903</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="K10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" t="s">
+        <v>29</v>
+      </c>
+      <c r="P10" t="s">
+        <v>39</v>
+      </c>
+      <c r="R10" t="s">
+        <v>67</v>
+      </c>
+      <c r="S10" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" t="s">
+        <v>28</v>
+      </c>
+      <c r="O11" t="s">
+        <v>29</v>
+      </c>
+      <c r="P11" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>24</v>
+      </c>
+      <c r="R11" t="s">
+        <v>67</v>
+      </c>
+      <c r="S11" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" t="s">
+        <v>907</v>
+      </c>
+      <c r="E12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" t="s">
+        <v>28</v>
+      </c>
+      <c r="O12" t="s">
+        <v>29</v>
+      </c>
+      <c r="P12" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>24</v>
+      </c>
+      <c r="R12" t="s">
+        <v>67</v>
+      </c>
+      <c r="S12" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="E13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" t="s">
+        <v>28</v>
+      </c>
+      <c r="O13" t="s">
+        <v>29</v>
+      </c>
+      <c r="P13" t="s">
+        <v>47</v>
+      </c>
+      <c r="R13" t="s">
+        <v>48</v>
+      </c>
+      <c r="S13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14" t="s">
+        <v>908</v>
+      </c>
+      <c r="E14" t="s">
+        <v>133</v>
+      </c>
+      <c r="F14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" t="s">
+        <v>28</v>
+      </c>
+      <c r="O14" t="s">
+        <v>29</v>
+      </c>
+      <c r="P14" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>24</v>
+      </c>
+      <c r="R14" t="s">
+        <v>67</v>
+      </c>
+      <c r="S14" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" t="s">
+        <v>161</v>
+      </c>
+      <c r="D15" t="s">
+        <v>909</v>
+      </c>
+      <c r="E15" t="s">
+        <v>163</v>
+      </c>
+      <c r="F15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" t="s">
+        <v>28</v>
+      </c>
+      <c r="O15" t="s">
+        <v>29</v>
+      </c>
+      <c r="P15" t="s">
+        <v>39</v>
+      </c>
+      <c r="R15" t="s">
+        <v>67</v>
+      </c>
+      <c r="S15" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>172</v>
+      </c>
+      <c r="B16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C16" t="s">
+        <v>174</v>
+      </c>
+      <c r="D16" t="s">
+        <v>910</v>
+      </c>
+      <c r="E16" t="s">
+        <v>176</v>
+      </c>
+      <c r="F16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" t="s">
+        <v>28</v>
+      </c>
+      <c r="O16" t="s">
+        <v>29</v>
+      </c>
+      <c r="P16" t="s">
+        <v>39</v>
+      </c>
+      <c r="R16" t="s">
+        <v>67</v>
+      </c>
+      <c r="S16" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>913</v>
+      </c>
+      <c r="B17" t="s">
+        <v>916</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="E17" t="s">
+        <v>915</v>
+      </c>
+      <c r="K17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O17" t="s">
+        <v>29</v>
+      </c>
+      <c r="P17" t="s">
+        <v>39</v>
+      </c>
+      <c r="R17" t="s">
+        <v>67</v>
+      </c>
+      <c r="S17" t="s">
+        <v>912</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{518B4BCD-31E9-4C65-84BF-DE9D60C684A3}"/>
+    <hyperlink ref="D4" r:id="rId2" xr:uid="{71C0E5B9-BAD0-471A-844C-8AB71332C4DF}"/>
+    <hyperlink ref="D5" r:id="rId3" xr:uid="{86ADB77B-0919-4E33-8E55-B5D58CB5D47B}"/>
+    <hyperlink ref="D6" r:id="rId4" xr:uid="{7911458F-6C14-444E-9940-37F70411545B}"/>
+    <hyperlink ref="D7" r:id="rId5" xr:uid="{80588D54-98D5-487F-BE98-3F83434AD464}"/>
+    <hyperlink ref="D8" r:id="rId6" xr:uid="{FFCA0106-F54B-4931-8DA3-8CD4A75D6875}"/>
+    <hyperlink ref="D2" r:id="rId7" xr:uid="{34F9C9BB-3698-4061-930E-AAF165699479}"/>
+    <hyperlink ref="D9" r:id="rId8" xr:uid="{AC225B06-6220-46E1-9444-C2F2422D3A36}"/>
+    <hyperlink ref="D10" r:id="rId9" xr:uid="{6B67C16E-CA7A-48E1-B1E7-0A33B3EA2246}"/>
+    <hyperlink ref="D11" r:id="rId10" xr:uid="{1F606225-CA61-4EBC-8143-B60ECED0755C}"/>
+    <hyperlink ref="D13" r:id="rId11" xr:uid="{CC3B78E3-277B-4D12-A17E-CF42C64BA191}"/>
+    <hyperlink ref="C17" r:id="rId12" xr:uid="{0227BB3D-FABE-44E6-AE24-EA27DDA4B41F}"/>
+    <hyperlink ref="D17" r:id="rId13" xr:uid="{E77EDD61-58AF-46B5-9EA4-10AC38B7972D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="A1:S1" numberStoredAsText="1"/>
@@ -12419,28 +13410,28 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:S1"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.796875" customWidth="1"/>
-    <col min="2" max="2" width="16.796875" customWidth="1"/>
-    <col min="3" max="3" width="34.796875" customWidth="1"/>
-    <col min="4" max="4" width="40.796875" customWidth="1"/>
-    <col min="5" max="5" width="10.796875" customWidth="1"/>
-    <col min="6" max="6" width="24.796875" customWidth="1"/>
-    <col min="7" max="7" width="32.796875" customWidth="1"/>
-    <col min="8" max="8" width="24.796875" customWidth="1"/>
-    <col min="9" max="10" width="16.796875" customWidth="1"/>
-    <col min="11" max="11" width="22.796875" customWidth="1"/>
-    <col min="12" max="12" width="12.796875" customWidth="1"/>
-    <col min="13" max="13" width="18.796875" customWidth="1"/>
-    <col min="14" max="14" width="20.796875" customWidth="1"/>
-    <col min="15" max="15" width="10.796875" customWidth="1"/>
-    <col min="16" max="16" width="28.796875" customWidth="1"/>
-    <col min="17" max="18" width="50.796875" customWidth="1"/>
-    <col min="19" max="19" width="40.796875" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="32.83203125" customWidth="1"/>
+    <col min="8" max="8" width="24.83203125" customWidth="1"/>
+    <col min="9" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="18.83203125" customWidth="1"/>
+    <col min="14" max="14" width="20.83203125" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" customWidth="1"/>
+    <col min="16" max="16" width="28.83203125" customWidth="1"/>
+    <col min="17" max="18" width="50.83203125" customWidth="1"/>
+    <col min="19" max="19" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
